--- a/Quarter/Quarterly_Jevons_Index_Results.xlsx
+++ b/Quarter/Quarterly_Jevons_Index_Results.xlsx
@@ -10,7 +10,8 @@
     <sheet name="Adjacent Quarters" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="All Quarter Pairs" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Same Quarter Across Years" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Model_Period_Matrix" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Summary" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -12366,6 +12367,8186 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:EW27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone XS Max 64GB</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone XS Max 256GB</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone XS Max 512GB</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone XR 64GB</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone XR 256GB</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone XR 128GB</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone XS 64GB</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone XS 256GB</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Note 10 256GB</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Note 10+ 512GB</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 11 64GB</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 11 128GB</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 11 Pro 64GB</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 11 256GB</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 11 Pro 256GB</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 11 Pro Max 512GB</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 11 Pro Max 64GB</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 11 Pro 512GB</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 11 Pro Max 256GB</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Find N2 Flip 256GB</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Note 10+ 256GB</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone XS 512GB</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus 7 Pro 5G 256GB</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus 8 Pro 256GB</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Note 20 Ultra 128GB</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 12 Pro Max 256GB</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 12 Pro Max 128GB</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 12 Pro Max 512GB</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 12 Pro 128GB</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 12 Pro 512GB</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 12 Pro 256GB</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 12 mini 128GB</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 12 64GB</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 12 128GB</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 12 256GB</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 12 mini 256GB</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 12 mini 64GB</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus 8 128GB</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus Nord N10 5G 128GB</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus 9 Pro 256GB</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus 9 128GB</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Note 20 128GB</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus Nord 2 5G 128GB</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus Nord N200 64GB</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus Nord N100 5G 64GB</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 13 mini 512GB</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 13 mini 256GB</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 13 mini 128GB</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 13 256GB</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 13 128GB</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 13 512GB</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 13 Pro 512GB</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 13 Pro Max 512GB</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 13 Pro 128GB</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 13 Pro Max 128GB</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 13 Pro 256GB</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 13 Pro Max 256GB</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus 8T 256GB</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno7 Pro 5G 256GB</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Find X5 256GB</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Find X5 Pro 256GB</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S22 128GB</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno7 5G 256GB</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S22 Ultra 128GB</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S22+ 128GB</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S22 256GB</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus Nord 2T 128GB</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno8 5G 128GB</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Xcover 5 64GB</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S22 Ultra 256GB</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S22+ 256GB</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno8 Pro 5G 256GB</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus 10 Pro 256GB</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Z Fold 4 256GB</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno8 5G 256GB</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno7 5G 128GB</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Z Fold 4 512GB</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Z Flip 4 256GB</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Z Flip 4 512GB</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 14 128GB</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 14 256GB</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 14 512GB</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 14 Pro Max 256GB</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 14 Plus 128GB</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 14 Pro Max 128GB</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 14 Plus 256GB</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 14 Pro Max 512GB</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 14 Pro 128GB</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 14 Pro 256GB</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 14 Pro 512GB</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 14 Plus 512GB</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus 11 256GB</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Xcover 6 Pro 128GB</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy A04 64GB</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy A34 256GB</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus Nord CE 3 Lite 256GB</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy A24 128GB</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy A54 128GB</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S23+ 256GB</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S23 Ultra 256GB</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S23 128GB</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy A54 256GB</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S23 256GB</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus 10T 5G 256GB</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno10 5G 256GB</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno10 Pro 5G 256GB</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Z Flip 5 512GB</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Z Fold 5 512GB</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus Nord N30 5G 128GB</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S24 128GB</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S24 256GB</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 15 256GB</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 15 512GB</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 15 128GB</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 15 Plus 512GB</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 15 Plus 256GB</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 15 Plus 128GB</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 15 Pro 512GB</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 15 Pro Max 512GB</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 15 Pro Max 256GB</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 15 Pro 128GB</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 15 Pro 256GB</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Z Flip 5 256GB</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus 12R 256GB</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno11 Pro 512GB</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno11 F 256GB</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - A60 256GB</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>OnePlus - OnePlus 12 256GB</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S24 Ultra 256GB</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone X 64GB</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy S24+ 256GB</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno12 256GB</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno12 Pro 512GB</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno12 F 4G 256GB</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - A80 256GB</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>Samsung - Galaxy Z Fold 5 256GB</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 16 256GB</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 16 Pro 512GB</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 16 Plus 512GB</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 16 Plus 256GB</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 16 Pro Max 256GB</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 16 Plus 128GB</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 16 Pro 256GB</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 16 Pro 128GB</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 16 128GB</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 16 512GB</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Find X8 Pro 512GB</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>Apple - iPhone 16 Pro Max 512GB</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno13 F 4G 256GB</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno13 256GB</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - Reno13 Pro 512GB</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>Oppo - A60 128GB</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>2018 Q4→2019 Q1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.1453484201187774</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.1662460317429311</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="inlineStr"/>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="inlineStr"/>
+      <c r="CA2" t="inlineStr"/>
+      <c r="CB2" t="inlineStr"/>
+      <c r="CC2" t="inlineStr"/>
+      <c r="CD2" t="inlineStr"/>
+      <c r="CE2" t="inlineStr"/>
+      <c r="CF2" t="inlineStr"/>
+      <c r="CG2" t="inlineStr"/>
+      <c r="CH2" t="inlineStr"/>
+      <c r="CI2" t="inlineStr"/>
+      <c r="CJ2" t="inlineStr"/>
+      <c r="CK2" t="inlineStr"/>
+      <c r="CL2" t="inlineStr"/>
+      <c r="CM2" t="inlineStr"/>
+      <c r="CN2" t="inlineStr"/>
+      <c r="CO2" t="inlineStr"/>
+      <c r="CP2" t="inlineStr"/>
+      <c r="CQ2" t="inlineStr"/>
+      <c r="CR2" t="inlineStr"/>
+      <c r="CS2" t="inlineStr"/>
+      <c r="CT2" t="inlineStr"/>
+      <c r="CU2" t="inlineStr"/>
+      <c r="CV2" t="inlineStr"/>
+      <c r="CW2" t="inlineStr"/>
+      <c r="CX2" t="inlineStr"/>
+      <c r="CY2" t="inlineStr"/>
+      <c r="CZ2" t="inlineStr"/>
+      <c r="DA2" t="inlineStr"/>
+      <c r="DB2" t="inlineStr"/>
+      <c r="DC2" t="inlineStr"/>
+      <c r="DD2" t="inlineStr"/>
+      <c r="DE2" t="inlineStr"/>
+      <c r="DF2" t="inlineStr"/>
+      <c r="DG2" t="inlineStr"/>
+      <c r="DH2" t="inlineStr"/>
+      <c r="DI2" t="inlineStr"/>
+      <c r="DJ2" t="inlineStr"/>
+      <c r="DK2" t="inlineStr"/>
+      <c r="DL2" t="inlineStr"/>
+      <c r="DM2" t="inlineStr"/>
+      <c r="DN2" t="inlineStr"/>
+      <c r="DO2" t="inlineStr"/>
+      <c r="DP2" t="inlineStr"/>
+      <c r="DQ2" t="inlineStr"/>
+      <c r="DR2" t="inlineStr"/>
+      <c r="DS2" t="inlineStr"/>
+      <c r="DT2" t="inlineStr"/>
+      <c r="DU2" t="inlineStr"/>
+      <c r="DV2" t="inlineStr"/>
+      <c r="DW2" t="inlineStr"/>
+      <c r="DX2" t="inlineStr"/>
+      <c r="DY2" t="inlineStr"/>
+      <c r="DZ2" t="inlineStr"/>
+      <c r="EA2" t="inlineStr"/>
+      <c r="EB2" t="inlineStr"/>
+      <c r="EC2" t="inlineStr"/>
+      <c r="ED2" t="inlineStr"/>
+      <c r="EE2" t="inlineStr"/>
+      <c r="EF2" t="inlineStr"/>
+      <c r="EG2" t="inlineStr"/>
+      <c r="EH2" t="inlineStr"/>
+      <c r="EI2" t="inlineStr"/>
+      <c r="EJ2" t="inlineStr"/>
+      <c r="EK2" t="inlineStr"/>
+      <c r="EL2" t="inlineStr"/>
+      <c r="EM2" t="inlineStr"/>
+      <c r="EN2" t="inlineStr"/>
+      <c r="EO2" t="inlineStr"/>
+      <c r="EP2" t="inlineStr"/>
+      <c r="EQ2" t="inlineStr"/>
+      <c r="ER2" t="inlineStr"/>
+      <c r="ES2" t="inlineStr"/>
+      <c r="ET2" t="inlineStr"/>
+      <c r="EU2" t="inlineStr"/>
+      <c r="EV2" t="inlineStr"/>
+      <c r="EW2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>2019 Q1→2019 Q2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>-0.1044712393811364</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.03291064120619325</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>-0.03642807725635944</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.05026994488754521</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr"/>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
+      <c r="BO3" t="inlineStr"/>
+      <c r="BP3" t="inlineStr"/>
+      <c r="BQ3" t="inlineStr"/>
+      <c r="BR3" t="inlineStr"/>
+      <c r="BS3" t="inlineStr"/>
+      <c r="BT3" t="inlineStr"/>
+      <c r="BU3" t="inlineStr"/>
+      <c r="BV3" t="inlineStr"/>
+      <c r="BW3" t="inlineStr"/>
+      <c r="BX3" t="inlineStr"/>
+      <c r="BY3" t="inlineStr"/>
+      <c r="BZ3" t="inlineStr"/>
+      <c r="CA3" t="inlineStr"/>
+      <c r="CB3" t="inlineStr"/>
+      <c r="CC3" t="inlineStr"/>
+      <c r="CD3" t="inlineStr"/>
+      <c r="CE3" t="inlineStr"/>
+      <c r="CF3" t="inlineStr"/>
+      <c r="CG3" t="inlineStr"/>
+      <c r="CH3" t="inlineStr"/>
+      <c r="CI3" t="inlineStr"/>
+      <c r="CJ3" t="inlineStr"/>
+      <c r="CK3" t="inlineStr"/>
+      <c r="CL3" t="inlineStr"/>
+      <c r="CM3" t="inlineStr"/>
+      <c r="CN3" t="inlineStr"/>
+      <c r="CO3" t="inlineStr"/>
+      <c r="CP3" t="inlineStr"/>
+      <c r="CQ3" t="inlineStr"/>
+      <c r="CR3" t="inlineStr"/>
+      <c r="CS3" t="inlineStr"/>
+      <c r="CT3" t="inlineStr"/>
+      <c r="CU3" t="inlineStr"/>
+      <c r="CV3" t="inlineStr"/>
+      <c r="CW3" t="inlineStr"/>
+      <c r="CX3" t="inlineStr"/>
+      <c r="CY3" t="inlineStr"/>
+      <c r="CZ3" t="inlineStr"/>
+      <c r="DA3" t="inlineStr"/>
+      <c r="DB3" t="inlineStr"/>
+      <c r="DC3" t="inlineStr"/>
+      <c r="DD3" t="inlineStr"/>
+      <c r="DE3" t="inlineStr"/>
+      <c r="DF3" t="inlineStr"/>
+      <c r="DG3" t="inlineStr"/>
+      <c r="DH3" t="inlineStr"/>
+      <c r="DI3" t="inlineStr"/>
+      <c r="DJ3" t="inlineStr"/>
+      <c r="DK3" t="inlineStr"/>
+      <c r="DL3" t="inlineStr"/>
+      <c r="DM3" t="inlineStr"/>
+      <c r="DN3" t="inlineStr"/>
+      <c r="DO3" t="inlineStr"/>
+      <c r="DP3" t="inlineStr"/>
+      <c r="DQ3" t="inlineStr"/>
+      <c r="DR3" t="inlineStr"/>
+      <c r="DS3" t="inlineStr"/>
+      <c r="DT3" t="inlineStr"/>
+      <c r="DU3" t="inlineStr"/>
+      <c r="DV3" t="inlineStr"/>
+      <c r="DW3" t="inlineStr"/>
+      <c r="DX3" t="inlineStr"/>
+      <c r="DY3" t="inlineStr"/>
+      <c r="DZ3" t="inlineStr"/>
+      <c r="EA3" t="inlineStr"/>
+      <c r="EB3" t="inlineStr"/>
+      <c r="EC3" t="inlineStr"/>
+      <c r="ED3" t="inlineStr"/>
+      <c r="EE3" t="inlineStr"/>
+      <c r="EF3" t="inlineStr"/>
+      <c r="EG3" t="inlineStr"/>
+      <c r="EH3" t="inlineStr"/>
+      <c r="EI3" t="inlineStr"/>
+      <c r="EJ3" t="inlineStr"/>
+      <c r="EK3" t="inlineStr"/>
+      <c r="EL3" t="inlineStr"/>
+      <c r="EM3" t="inlineStr"/>
+      <c r="EN3" t="inlineStr"/>
+      <c r="EO3" t="inlineStr"/>
+      <c r="EP3" t="inlineStr"/>
+      <c r="EQ3" t="inlineStr"/>
+      <c r="ER3" t="inlineStr"/>
+      <c r="ES3" t="inlineStr"/>
+      <c r="ET3" t="inlineStr"/>
+      <c r="EU3" t="inlineStr"/>
+      <c r="EV3" t="inlineStr"/>
+      <c r="EW3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>2019 Q2→2019 Q3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>-0.1116905756477902</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.1681213566233088</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.2523340022826206</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.01196130765806558</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.01110393030868018</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.01698843909857661</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.07167380440077231</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-0.1272261700825217</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
+      <c r="BO4" t="inlineStr"/>
+      <c r="BP4" t="inlineStr"/>
+      <c r="BQ4" t="inlineStr"/>
+      <c r="BR4" t="inlineStr"/>
+      <c r="BS4" t="inlineStr"/>
+      <c r="BT4" t="inlineStr"/>
+      <c r="BU4" t="inlineStr"/>
+      <c r="BV4" t="inlineStr"/>
+      <c r="BW4" t="inlineStr"/>
+      <c r="BX4" t="inlineStr"/>
+      <c r="BY4" t="inlineStr"/>
+      <c r="BZ4" t="inlineStr"/>
+      <c r="CA4" t="inlineStr"/>
+      <c r="CB4" t="inlineStr"/>
+      <c r="CC4" t="inlineStr"/>
+      <c r="CD4" t="inlineStr"/>
+      <c r="CE4" t="inlineStr"/>
+      <c r="CF4" t="inlineStr"/>
+      <c r="CG4" t="inlineStr"/>
+      <c r="CH4" t="inlineStr"/>
+      <c r="CI4" t="inlineStr"/>
+      <c r="CJ4" t="inlineStr"/>
+      <c r="CK4" t="inlineStr"/>
+      <c r="CL4" t="inlineStr"/>
+      <c r="CM4" t="inlineStr"/>
+      <c r="CN4" t="inlineStr"/>
+      <c r="CO4" t="inlineStr"/>
+      <c r="CP4" t="inlineStr"/>
+      <c r="CQ4" t="inlineStr"/>
+      <c r="CR4" t="inlineStr"/>
+      <c r="CS4" t="inlineStr"/>
+      <c r="CT4" t="inlineStr"/>
+      <c r="CU4" t="inlineStr"/>
+      <c r="CV4" t="inlineStr"/>
+      <c r="CW4" t="inlineStr"/>
+      <c r="CX4" t="inlineStr"/>
+      <c r="CY4" t="inlineStr"/>
+      <c r="CZ4" t="inlineStr"/>
+      <c r="DA4" t="inlineStr"/>
+      <c r="DB4" t="inlineStr"/>
+      <c r="DC4" t="inlineStr"/>
+      <c r="DD4" t="inlineStr"/>
+      <c r="DE4" t="inlineStr"/>
+      <c r="DF4" t="inlineStr"/>
+      <c r="DG4" t="inlineStr"/>
+      <c r="DH4" t="inlineStr"/>
+      <c r="DI4" t="inlineStr"/>
+      <c r="DJ4" t="inlineStr"/>
+      <c r="DK4" t="inlineStr"/>
+      <c r="DL4" t="inlineStr"/>
+      <c r="DM4" t="inlineStr"/>
+      <c r="DN4" t="inlineStr"/>
+      <c r="DO4" t="inlineStr"/>
+      <c r="DP4" t="inlineStr"/>
+      <c r="DQ4" t="inlineStr"/>
+      <c r="DR4" t="inlineStr"/>
+      <c r="DS4" t="inlineStr"/>
+      <c r="DT4" t="inlineStr"/>
+      <c r="DU4" t="inlineStr"/>
+      <c r="DV4" t="inlineStr"/>
+      <c r="DW4" t="inlineStr"/>
+      <c r="DX4" t="inlineStr"/>
+      <c r="DY4" t="inlineStr"/>
+      <c r="DZ4" t="inlineStr"/>
+      <c r="EA4" t="inlineStr"/>
+      <c r="EB4" t="inlineStr"/>
+      <c r="EC4" t="inlineStr"/>
+      <c r="ED4" t="inlineStr"/>
+      <c r="EE4" t="inlineStr"/>
+      <c r="EF4" t="inlineStr"/>
+      <c r="EG4" t="inlineStr"/>
+      <c r="EH4" t="inlineStr"/>
+      <c r="EI4" t="inlineStr"/>
+      <c r="EJ4" t="inlineStr"/>
+      <c r="EK4" t="inlineStr"/>
+      <c r="EL4" t="inlineStr"/>
+      <c r="EM4" t="inlineStr"/>
+      <c r="EN4" t="inlineStr"/>
+      <c r="EO4" t="inlineStr"/>
+      <c r="EP4" t="inlineStr"/>
+      <c r="EQ4" t="inlineStr"/>
+      <c r="ER4" t="inlineStr"/>
+      <c r="ES4" t="inlineStr"/>
+      <c r="ET4" t="inlineStr"/>
+      <c r="EU4" t="inlineStr"/>
+      <c r="EV4" t="inlineStr"/>
+      <c r="EW4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>2019 Q3→2019 Q4</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>-0.3196210224827807</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.3825892715975252</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.3176571596570321</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.2032421083126872</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.1666058461236251</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.2333478982158717</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.2521887089517714</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0.2470680305067257</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr"/>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr"/>
+      <c r="BO5" t="inlineStr"/>
+      <c r="BP5" t="inlineStr"/>
+      <c r="BQ5" t="inlineStr"/>
+      <c r="BR5" t="inlineStr"/>
+      <c r="BS5" t="inlineStr"/>
+      <c r="BT5" t="inlineStr"/>
+      <c r="BU5" t="inlineStr"/>
+      <c r="BV5" t="inlineStr"/>
+      <c r="BW5" t="inlineStr"/>
+      <c r="BX5" t="inlineStr"/>
+      <c r="BY5" t="inlineStr"/>
+      <c r="BZ5" t="inlineStr"/>
+      <c r="CA5" t="inlineStr"/>
+      <c r="CB5" t="inlineStr"/>
+      <c r="CC5" t="inlineStr"/>
+      <c r="CD5" t="inlineStr"/>
+      <c r="CE5" t="inlineStr"/>
+      <c r="CF5" t="inlineStr"/>
+      <c r="CG5" t="inlineStr"/>
+      <c r="CH5" t="inlineStr"/>
+      <c r="CI5" t="inlineStr"/>
+      <c r="CJ5" t="inlineStr"/>
+      <c r="CK5" t="inlineStr"/>
+      <c r="CL5" t="inlineStr"/>
+      <c r="CM5" t="inlineStr"/>
+      <c r="CN5" t="inlineStr"/>
+      <c r="CO5" t="inlineStr"/>
+      <c r="CP5" t="inlineStr"/>
+      <c r="CQ5" t="inlineStr"/>
+      <c r="CR5" t="inlineStr"/>
+      <c r="CS5" t="inlineStr"/>
+      <c r="CT5" t="inlineStr"/>
+      <c r="CU5" t="inlineStr"/>
+      <c r="CV5" t="inlineStr"/>
+      <c r="CW5" t="inlineStr"/>
+      <c r="CX5" t="inlineStr"/>
+      <c r="CY5" t="inlineStr"/>
+      <c r="CZ5" t="inlineStr"/>
+      <c r="DA5" t="inlineStr"/>
+      <c r="DB5" t="inlineStr"/>
+      <c r="DC5" t="inlineStr"/>
+      <c r="DD5" t="inlineStr"/>
+      <c r="DE5" t="inlineStr"/>
+      <c r="DF5" t="inlineStr"/>
+      <c r="DG5" t="inlineStr"/>
+      <c r="DH5" t="inlineStr"/>
+      <c r="DI5" t="inlineStr"/>
+      <c r="DJ5" t="inlineStr"/>
+      <c r="DK5" t="inlineStr"/>
+      <c r="DL5" t="inlineStr"/>
+      <c r="DM5" t="inlineStr"/>
+      <c r="DN5" t="inlineStr"/>
+      <c r="DO5" t="inlineStr"/>
+      <c r="DP5" t="inlineStr"/>
+      <c r="DQ5" t="inlineStr"/>
+      <c r="DR5" t="inlineStr"/>
+      <c r="DS5" t="inlineStr"/>
+      <c r="DT5" t="inlineStr"/>
+      <c r="DU5" t="inlineStr"/>
+      <c r="DV5" t="inlineStr"/>
+      <c r="DW5" t="inlineStr"/>
+      <c r="DX5" t="inlineStr"/>
+      <c r="DY5" t="inlineStr"/>
+      <c r="DZ5" t="inlineStr"/>
+      <c r="EA5" t="inlineStr"/>
+      <c r="EB5" t="inlineStr"/>
+      <c r="EC5" t="inlineStr"/>
+      <c r="ED5" t="inlineStr"/>
+      <c r="EE5" t="inlineStr"/>
+      <c r="EF5" t="inlineStr"/>
+      <c r="EG5" t="inlineStr"/>
+      <c r="EH5" t="inlineStr"/>
+      <c r="EI5" t="inlineStr"/>
+      <c r="EJ5" t="inlineStr"/>
+      <c r="EK5" t="inlineStr"/>
+      <c r="EL5" t="inlineStr"/>
+      <c r="EM5" t="inlineStr"/>
+      <c r="EN5" t="inlineStr"/>
+      <c r="EO5" t="inlineStr"/>
+      <c r="EP5" t="inlineStr"/>
+      <c r="EQ5" t="inlineStr"/>
+      <c r="ER5" t="inlineStr"/>
+      <c r="ES5" t="inlineStr"/>
+      <c r="ET5" t="inlineStr"/>
+      <c r="EU5" t="inlineStr"/>
+      <c r="EV5" t="inlineStr"/>
+      <c r="EW5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>2019 Q4→2020 Q1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-0.203189893300161</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.1750409667996538</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.209666305713788</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.1470016590789136</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.174148018464491</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.1336159476537322</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.1937587774397285</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-0.2348084227060641</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-0.1771026943866865</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0.04018954204536307</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-0.07106622709824961</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-0.0007674148253551394</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.02022747481265963</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.02732355392706953</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.03228282932435622</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1818826266940405</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.02340332757470787</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.1079844185914531</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.000401323586294744</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="inlineStr"/>
+      <c r="BP6" t="inlineStr"/>
+      <c r="BQ6" t="inlineStr"/>
+      <c r="BR6" t="inlineStr"/>
+      <c r="BS6" t="inlineStr"/>
+      <c r="BT6" t="inlineStr"/>
+      <c r="BU6" t="inlineStr"/>
+      <c r="BV6" t="inlineStr"/>
+      <c r="BW6" t="inlineStr"/>
+      <c r="BX6" t="inlineStr"/>
+      <c r="BY6" t="inlineStr"/>
+      <c r="BZ6" t="inlineStr"/>
+      <c r="CA6" t="inlineStr"/>
+      <c r="CB6" t="inlineStr"/>
+      <c r="CC6" t="inlineStr"/>
+      <c r="CD6" t="inlineStr"/>
+      <c r="CE6" t="inlineStr"/>
+      <c r="CF6" t="inlineStr"/>
+      <c r="CG6" t="inlineStr"/>
+      <c r="CH6" t="inlineStr"/>
+      <c r="CI6" t="inlineStr"/>
+      <c r="CJ6" t="inlineStr"/>
+      <c r="CK6" t="inlineStr"/>
+      <c r="CL6" t="inlineStr"/>
+      <c r="CM6" t="inlineStr"/>
+      <c r="CN6" t="inlineStr"/>
+      <c r="CO6" t="inlineStr"/>
+      <c r="CP6" t="inlineStr"/>
+      <c r="CQ6" t="inlineStr"/>
+      <c r="CR6" t="inlineStr"/>
+      <c r="CS6" t="inlineStr"/>
+      <c r="CT6" t="inlineStr"/>
+      <c r="CU6" t="inlineStr"/>
+      <c r="CV6" t="inlineStr"/>
+      <c r="CW6" t="inlineStr"/>
+      <c r="CX6" t="inlineStr"/>
+      <c r="CY6" t="inlineStr"/>
+      <c r="CZ6" t="inlineStr"/>
+      <c r="DA6" t="inlineStr"/>
+      <c r="DB6" t="inlineStr"/>
+      <c r="DC6" t="inlineStr"/>
+      <c r="DD6" t="inlineStr"/>
+      <c r="DE6" t="inlineStr"/>
+      <c r="DF6" t="inlineStr"/>
+      <c r="DG6" t="inlineStr"/>
+      <c r="DH6" t="inlineStr"/>
+      <c r="DI6" t="inlineStr"/>
+      <c r="DJ6" t="inlineStr"/>
+      <c r="DK6" t="inlineStr"/>
+      <c r="DL6" t="inlineStr"/>
+      <c r="DM6" t="inlineStr"/>
+      <c r="DN6" t="inlineStr"/>
+      <c r="DO6" t="inlineStr"/>
+      <c r="DP6" t="inlineStr"/>
+      <c r="DQ6" t="inlineStr"/>
+      <c r="DR6" t="inlineStr"/>
+      <c r="DS6" t="inlineStr"/>
+      <c r="DT6" t="inlineStr"/>
+      <c r="DU6" t="inlineStr"/>
+      <c r="DV6" t="inlineStr"/>
+      <c r="DW6" t="inlineStr"/>
+      <c r="DX6" t="inlineStr"/>
+      <c r="DY6" t="inlineStr"/>
+      <c r="DZ6" t="inlineStr"/>
+      <c r="EA6" t="inlineStr"/>
+      <c r="EB6" t="inlineStr"/>
+      <c r="EC6" t="inlineStr"/>
+      <c r="ED6" t="inlineStr"/>
+      <c r="EE6" t="inlineStr"/>
+      <c r="EF6" t="inlineStr"/>
+      <c r="EG6" t="inlineStr"/>
+      <c r="EH6" t="inlineStr"/>
+      <c r="EI6" t="inlineStr"/>
+      <c r="EJ6" t="inlineStr"/>
+      <c r="EK6" t="inlineStr"/>
+      <c r="EL6" t="inlineStr"/>
+      <c r="EM6" t="inlineStr"/>
+      <c r="EN6" t="inlineStr"/>
+      <c r="EO6" t="inlineStr"/>
+      <c r="EP6" t="inlineStr"/>
+      <c r="EQ6" t="inlineStr"/>
+      <c r="ER6" t="inlineStr"/>
+      <c r="ES6" t="inlineStr"/>
+      <c r="ET6" t="inlineStr"/>
+      <c r="EU6" t="inlineStr"/>
+      <c r="EV6" t="inlineStr"/>
+      <c r="EW6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>2020 Q1→2020 Q2</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>-0.07623035321795424</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.02438691219506239</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.06719382281648834</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.03255939175127587</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.07111776619016563</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.02584640822787954</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.03909279461668458</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.00662548953300135</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.005795416580224533</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.1016347555716584</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.05424521163014084</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-0.05592532844630682</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.1399783897464211</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.1981279413050094</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0.2233784837211514</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.3173605215683875</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-0.1585761937380257</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.3368358979447459</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0.1620585546890334</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0.006713599715282292</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.1956421412220042</v>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr"/>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="inlineStr"/>
+      <c r="BM7" t="inlineStr"/>
+      <c r="BN7" t="inlineStr"/>
+      <c r="BO7" t="inlineStr"/>
+      <c r="BP7" t="inlineStr"/>
+      <c r="BQ7" t="inlineStr"/>
+      <c r="BR7" t="inlineStr"/>
+      <c r="BS7" t="inlineStr"/>
+      <c r="BT7" t="inlineStr"/>
+      <c r="BU7" t="inlineStr"/>
+      <c r="BV7" t="inlineStr"/>
+      <c r="BW7" t="inlineStr"/>
+      <c r="BX7" t="inlineStr"/>
+      <c r="BY7" t="inlineStr"/>
+      <c r="BZ7" t="inlineStr"/>
+      <c r="CA7" t="inlineStr"/>
+      <c r="CB7" t="inlineStr"/>
+      <c r="CC7" t="inlineStr"/>
+      <c r="CD7" t="inlineStr"/>
+      <c r="CE7" t="inlineStr"/>
+      <c r="CF7" t="inlineStr"/>
+      <c r="CG7" t="inlineStr"/>
+      <c r="CH7" t="inlineStr"/>
+      <c r="CI7" t="inlineStr"/>
+      <c r="CJ7" t="inlineStr"/>
+      <c r="CK7" t="inlineStr"/>
+      <c r="CL7" t="inlineStr"/>
+      <c r="CM7" t="inlineStr"/>
+      <c r="CN7" t="inlineStr"/>
+      <c r="CO7" t="inlineStr"/>
+      <c r="CP7" t="inlineStr"/>
+      <c r="CQ7" t="inlineStr"/>
+      <c r="CR7" t="inlineStr"/>
+      <c r="CS7" t="inlineStr"/>
+      <c r="CT7" t="inlineStr"/>
+      <c r="CU7" t="inlineStr"/>
+      <c r="CV7" t="inlineStr"/>
+      <c r="CW7" t="inlineStr"/>
+      <c r="CX7" t="inlineStr"/>
+      <c r="CY7" t="inlineStr"/>
+      <c r="CZ7" t="inlineStr"/>
+      <c r="DA7" t="inlineStr"/>
+      <c r="DB7" t="inlineStr"/>
+      <c r="DC7" t="inlineStr"/>
+      <c r="DD7" t="inlineStr"/>
+      <c r="DE7" t="inlineStr"/>
+      <c r="DF7" t="inlineStr"/>
+      <c r="DG7" t="inlineStr"/>
+      <c r="DH7" t="inlineStr"/>
+      <c r="DI7" t="inlineStr"/>
+      <c r="DJ7" t="inlineStr"/>
+      <c r="DK7" t="inlineStr"/>
+      <c r="DL7" t="inlineStr"/>
+      <c r="DM7" t="inlineStr"/>
+      <c r="DN7" t="inlineStr"/>
+      <c r="DO7" t="inlineStr"/>
+      <c r="DP7" t="inlineStr"/>
+      <c r="DQ7" t="inlineStr"/>
+      <c r="DR7" t="inlineStr"/>
+      <c r="DS7" t="inlineStr"/>
+      <c r="DT7" t="inlineStr"/>
+      <c r="DU7" t="inlineStr"/>
+      <c r="DV7" t="inlineStr"/>
+      <c r="DW7" t="inlineStr"/>
+      <c r="DX7" t="inlineStr"/>
+      <c r="DY7" t="inlineStr"/>
+      <c r="DZ7" t="inlineStr"/>
+      <c r="EA7" t="inlineStr"/>
+      <c r="EB7" t="inlineStr"/>
+      <c r="EC7" t="inlineStr"/>
+      <c r="ED7" t="inlineStr"/>
+      <c r="EE7" t="inlineStr"/>
+      <c r="EF7" t="inlineStr"/>
+      <c r="EG7" t="inlineStr"/>
+      <c r="EH7" t="inlineStr"/>
+      <c r="EI7" t="inlineStr"/>
+      <c r="EJ7" t="inlineStr"/>
+      <c r="EK7" t="inlineStr"/>
+      <c r="EL7" t="inlineStr"/>
+      <c r="EM7" t="inlineStr"/>
+      <c r="EN7" t="inlineStr"/>
+      <c r="EO7" t="inlineStr"/>
+      <c r="EP7" t="inlineStr"/>
+      <c r="EQ7" t="inlineStr"/>
+      <c r="ER7" t="inlineStr"/>
+      <c r="ES7" t="inlineStr"/>
+      <c r="ET7" t="inlineStr"/>
+      <c r="EU7" t="inlineStr"/>
+      <c r="EV7" t="inlineStr"/>
+      <c r="EW7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>2020 Q2→2020 Q3</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.0615884075902029</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.05171878254742168</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.09623701892563652</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.01879098647413002</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.04355115176915891</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.01150513841287903</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.0078521587805227</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.04795041533435906</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.1203723543431359</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.1341457223803753</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.02864135892906194</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.02091579514997299</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0.0807535290123953</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.03091028717437894</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0.07597918617654464</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.1274831211035439</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-0.02258723604153445</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0.08981898814962719</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0.0598662753452448</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.03240509377343237</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.1830917520157023</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.08674216127044065</v>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="inlineStr"/>
+      <c r="BM8" t="inlineStr"/>
+      <c r="BN8" t="inlineStr"/>
+      <c r="BO8" t="inlineStr"/>
+      <c r="BP8" t="inlineStr"/>
+      <c r="BQ8" t="inlineStr"/>
+      <c r="BR8" t="inlineStr"/>
+      <c r="BS8" t="inlineStr"/>
+      <c r="BT8" t="inlineStr"/>
+      <c r="BU8" t="inlineStr"/>
+      <c r="BV8" t="inlineStr"/>
+      <c r="BW8" t="inlineStr"/>
+      <c r="BX8" t="inlineStr"/>
+      <c r="BY8" t="inlineStr"/>
+      <c r="BZ8" t="inlineStr"/>
+      <c r="CA8" t="inlineStr"/>
+      <c r="CB8" t="inlineStr"/>
+      <c r="CC8" t="inlineStr"/>
+      <c r="CD8" t="inlineStr"/>
+      <c r="CE8" t="inlineStr"/>
+      <c r="CF8" t="inlineStr"/>
+      <c r="CG8" t="inlineStr"/>
+      <c r="CH8" t="inlineStr"/>
+      <c r="CI8" t="inlineStr"/>
+      <c r="CJ8" t="inlineStr"/>
+      <c r="CK8" t="inlineStr"/>
+      <c r="CL8" t="inlineStr"/>
+      <c r="CM8" t="inlineStr"/>
+      <c r="CN8" t="inlineStr"/>
+      <c r="CO8" t="inlineStr"/>
+      <c r="CP8" t="inlineStr"/>
+      <c r="CQ8" t="inlineStr"/>
+      <c r="CR8" t="inlineStr"/>
+      <c r="CS8" t="inlineStr"/>
+      <c r="CT8" t="inlineStr"/>
+      <c r="CU8" t="inlineStr"/>
+      <c r="CV8" t="inlineStr"/>
+      <c r="CW8" t="inlineStr"/>
+      <c r="CX8" t="inlineStr"/>
+      <c r="CY8" t="inlineStr"/>
+      <c r="CZ8" t="inlineStr"/>
+      <c r="DA8" t="inlineStr"/>
+      <c r="DB8" t="inlineStr"/>
+      <c r="DC8" t="inlineStr"/>
+      <c r="DD8" t="inlineStr"/>
+      <c r="DE8" t="inlineStr"/>
+      <c r="DF8" t="inlineStr"/>
+      <c r="DG8" t="inlineStr"/>
+      <c r="DH8" t="inlineStr"/>
+      <c r="DI8" t="inlineStr"/>
+      <c r="DJ8" t="inlineStr"/>
+      <c r="DK8" t="inlineStr"/>
+      <c r="DL8" t="inlineStr"/>
+      <c r="DM8" t="inlineStr"/>
+      <c r="DN8" t="inlineStr"/>
+      <c r="DO8" t="inlineStr"/>
+      <c r="DP8" t="inlineStr"/>
+      <c r="DQ8" t="inlineStr"/>
+      <c r="DR8" t="inlineStr"/>
+      <c r="DS8" t="inlineStr"/>
+      <c r="DT8" t="inlineStr"/>
+      <c r="DU8" t="inlineStr"/>
+      <c r="DV8" t="inlineStr"/>
+      <c r="DW8" t="inlineStr"/>
+      <c r="DX8" t="inlineStr"/>
+      <c r="DY8" t="inlineStr"/>
+      <c r="DZ8" t="inlineStr"/>
+      <c r="EA8" t="inlineStr"/>
+      <c r="EB8" t="inlineStr"/>
+      <c r="EC8" t="inlineStr"/>
+      <c r="ED8" t="inlineStr"/>
+      <c r="EE8" t="inlineStr"/>
+      <c r="EF8" t="inlineStr"/>
+      <c r="EG8" t="inlineStr"/>
+      <c r="EH8" t="inlineStr"/>
+      <c r="EI8" t="inlineStr"/>
+      <c r="EJ8" t="inlineStr"/>
+      <c r="EK8" t="inlineStr"/>
+      <c r="EL8" t="inlineStr"/>
+      <c r="EM8" t="inlineStr"/>
+      <c r="EN8" t="inlineStr"/>
+      <c r="EO8" t="inlineStr"/>
+      <c r="EP8" t="inlineStr"/>
+      <c r="EQ8" t="inlineStr"/>
+      <c r="ER8" t="inlineStr"/>
+      <c r="ES8" t="inlineStr"/>
+      <c r="ET8" t="inlineStr"/>
+      <c r="EU8" t="inlineStr"/>
+      <c r="EV8" t="inlineStr"/>
+      <c r="EW8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>2020 Q3→2020 Q4</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>-0.1210376755350611</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.1582525523388485</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.06552284503603456</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.1570757316222133</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.1493214309100548</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.1544743441019625</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.1039221936328572</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-0.1585852016930218</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0.1523877227871679</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-0.2478979204224867</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-0.1341932046044185</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.1302410561637952</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.09204670438177498</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0.08498647918657998</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0.0834635590449011</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0.05535566411777637</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-0.08814127251712289</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0.02456554518798804</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.04808908984746196</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>-0.1754328256095077</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.1255172818718329</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.2070586652081436</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0.05840127144678231</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.01753938606193373</v>
+      </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+      <c r="BO9" t="inlineStr"/>
+      <c r="BP9" t="inlineStr"/>
+      <c r="BQ9" t="inlineStr"/>
+      <c r="BR9" t="inlineStr"/>
+      <c r="BS9" t="inlineStr"/>
+      <c r="BT9" t="inlineStr"/>
+      <c r="BU9" t="inlineStr"/>
+      <c r="BV9" t="inlineStr"/>
+      <c r="BW9" t="inlineStr"/>
+      <c r="BX9" t="inlineStr"/>
+      <c r="BY9" t="inlineStr"/>
+      <c r="BZ9" t="inlineStr"/>
+      <c r="CA9" t="inlineStr"/>
+      <c r="CB9" t="inlineStr"/>
+      <c r="CC9" t="inlineStr"/>
+      <c r="CD9" t="inlineStr"/>
+      <c r="CE9" t="inlineStr"/>
+      <c r="CF9" t="inlineStr"/>
+      <c r="CG9" t="inlineStr"/>
+      <c r="CH9" t="inlineStr"/>
+      <c r="CI9" t="inlineStr"/>
+      <c r="CJ9" t="inlineStr"/>
+      <c r="CK9" t="inlineStr"/>
+      <c r="CL9" t="inlineStr"/>
+      <c r="CM9" t="inlineStr"/>
+      <c r="CN9" t="inlineStr"/>
+      <c r="CO9" t="inlineStr"/>
+      <c r="CP9" t="inlineStr"/>
+      <c r="CQ9" t="inlineStr"/>
+      <c r="CR9" t="inlineStr"/>
+      <c r="CS9" t="inlineStr"/>
+      <c r="CT9" t="inlineStr"/>
+      <c r="CU9" t="inlineStr"/>
+      <c r="CV9" t="inlineStr"/>
+      <c r="CW9" t="inlineStr"/>
+      <c r="CX9" t="inlineStr"/>
+      <c r="CY9" t="inlineStr"/>
+      <c r="CZ9" t="inlineStr"/>
+      <c r="DA9" t="inlineStr"/>
+      <c r="DB9" t="inlineStr"/>
+      <c r="DC9" t="inlineStr"/>
+      <c r="DD9" t="inlineStr"/>
+      <c r="DE9" t="inlineStr"/>
+      <c r="DF9" t="inlineStr"/>
+      <c r="DG9" t="inlineStr"/>
+      <c r="DH9" t="inlineStr"/>
+      <c r="DI9" t="inlineStr"/>
+      <c r="DJ9" t="inlineStr"/>
+      <c r="DK9" t="inlineStr"/>
+      <c r="DL9" t="inlineStr"/>
+      <c r="DM9" t="inlineStr"/>
+      <c r="DN9" t="inlineStr"/>
+      <c r="DO9" t="inlineStr"/>
+      <c r="DP9" t="inlineStr"/>
+      <c r="DQ9" t="inlineStr"/>
+      <c r="DR9" t="inlineStr"/>
+      <c r="DS9" t="inlineStr"/>
+      <c r="DT9" t="inlineStr"/>
+      <c r="DU9" t="inlineStr"/>
+      <c r="DV9" t="inlineStr"/>
+      <c r="DW9" t="inlineStr"/>
+      <c r="DX9" t="inlineStr"/>
+      <c r="DY9" t="inlineStr"/>
+      <c r="DZ9" t="inlineStr"/>
+      <c r="EA9" t="inlineStr"/>
+      <c r="EB9" t="inlineStr"/>
+      <c r="EC9" t="inlineStr"/>
+      <c r="ED9" t="inlineStr"/>
+      <c r="EE9" t="inlineStr"/>
+      <c r="EF9" t="inlineStr"/>
+      <c r="EG9" t="inlineStr"/>
+      <c r="EH9" t="inlineStr"/>
+      <c r="EI9" t="inlineStr"/>
+      <c r="EJ9" t="inlineStr"/>
+      <c r="EK9" t="inlineStr"/>
+      <c r="EL9" t="inlineStr"/>
+      <c r="EM9" t="inlineStr"/>
+      <c r="EN9" t="inlineStr"/>
+      <c r="EO9" t="inlineStr"/>
+      <c r="EP9" t="inlineStr"/>
+      <c r="EQ9" t="inlineStr"/>
+      <c r="ER9" t="inlineStr"/>
+      <c r="ES9" t="inlineStr"/>
+      <c r="ET9" t="inlineStr"/>
+      <c r="EU9" t="inlineStr"/>
+      <c r="EV9" t="inlineStr"/>
+      <c r="EW9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>2020 Q4→2021 Q1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.1302232869469311</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.131250497674797</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.1866311918267165</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.1289231147596803</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.09077238271849808</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.07369781395541342</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.2254626224630059</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.2079032683405666</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-0.08186646521302077</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.13803243325619</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.03162305120424325</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-0.06285960302141369</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.09379450150386059</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.02454454957917118</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.1038945225709238</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.1216782669418635</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-0.16344514821653</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-0.1298488939333469</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0.1259102854438083</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>-0.1302326863649261</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.1792123165110491</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.07967830716906033</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-0.09892851489440613</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0.1878987627491169</v>
+      </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+      <c r="BO10" t="inlineStr"/>
+      <c r="BP10" t="inlineStr"/>
+      <c r="BQ10" t="inlineStr"/>
+      <c r="BR10" t="inlineStr"/>
+      <c r="BS10" t="inlineStr"/>
+      <c r="BT10" t="inlineStr"/>
+      <c r="BU10" t="inlineStr"/>
+      <c r="BV10" t="inlineStr"/>
+      <c r="BW10" t="inlineStr"/>
+      <c r="BX10" t="inlineStr"/>
+      <c r="BY10" t="inlineStr"/>
+      <c r="BZ10" t="inlineStr"/>
+      <c r="CA10" t="inlineStr"/>
+      <c r="CB10" t="inlineStr"/>
+      <c r="CC10" t="inlineStr"/>
+      <c r="CD10" t="inlineStr"/>
+      <c r="CE10" t="inlineStr"/>
+      <c r="CF10" t="inlineStr"/>
+      <c r="CG10" t="inlineStr"/>
+      <c r="CH10" t="inlineStr"/>
+      <c r="CI10" t="inlineStr"/>
+      <c r="CJ10" t="inlineStr"/>
+      <c r="CK10" t="inlineStr"/>
+      <c r="CL10" t="inlineStr"/>
+      <c r="CM10" t="inlineStr"/>
+      <c r="CN10" t="inlineStr"/>
+      <c r="CO10" t="inlineStr"/>
+      <c r="CP10" t="inlineStr"/>
+      <c r="CQ10" t="inlineStr"/>
+      <c r="CR10" t="inlineStr"/>
+      <c r="CS10" t="inlineStr"/>
+      <c r="CT10" t="inlineStr"/>
+      <c r="CU10" t="inlineStr"/>
+      <c r="CV10" t="inlineStr"/>
+      <c r="CW10" t="inlineStr"/>
+      <c r="CX10" t="inlineStr"/>
+      <c r="CY10" t="inlineStr"/>
+      <c r="CZ10" t="inlineStr"/>
+      <c r="DA10" t="inlineStr"/>
+      <c r="DB10" t="inlineStr"/>
+      <c r="DC10" t="inlineStr"/>
+      <c r="DD10" t="inlineStr"/>
+      <c r="DE10" t="inlineStr"/>
+      <c r="DF10" t="inlineStr"/>
+      <c r="DG10" t="inlineStr"/>
+      <c r="DH10" t="inlineStr"/>
+      <c r="DI10" t="inlineStr"/>
+      <c r="DJ10" t="inlineStr"/>
+      <c r="DK10" t="inlineStr"/>
+      <c r="DL10" t="inlineStr"/>
+      <c r="DM10" t="inlineStr"/>
+      <c r="DN10" t="inlineStr"/>
+      <c r="DO10" t="inlineStr"/>
+      <c r="DP10" t="inlineStr"/>
+      <c r="DQ10" t="inlineStr"/>
+      <c r="DR10" t="inlineStr"/>
+      <c r="DS10" t="inlineStr"/>
+      <c r="DT10" t="inlineStr"/>
+      <c r="DU10" t="inlineStr"/>
+      <c r="DV10" t="inlineStr"/>
+      <c r="DW10" t="inlineStr"/>
+      <c r="DX10" t="inlineStr"/>
+      <c r="DY10" t="inlineStr"/>
+      <c r="DZ10" t="inlineStr"/>
+      <c r="EA10" t="inlineStr"/>
+      <c r="EB10" t="inlineStr"/>
+      <c r="EC10" t="inlineStr"/>
+      <c r="ED10" t="inlineStr"/>
+      <c r="EE10" t="inlineStr"/>
+      <c r="EF10" t="inlineStr"/>
+      <c r="EG10" t="inlineStr"/>
+      <c r="EH10" t="inlineStr"/>
+      <c r="EI10" t="inlineStr"/>
+      <c r="EJ10" t="inlineStr"/>
+      <c r="EK10" t="inlineStr"/>
+      <c r="EL10" t="inlineStr"/>
+      <c r="EM10" t="inlineStr"/>
+      <c r="EN10" t="inlineStr"/>
+      <c r="EO10" t="inlineStr"/>
+      <c r="EP10" t="inlineStr"/>
+      <c r="EQ10" t="inlineStr"/>
+      <c r="ER10" t="inlineStr"/>
+      <c r="ES10" t="inlineStr"/>
+      <c r="ET10" t="inlineStr"/>
+      <c r="EU10" t="inlineStr"/>
+      <c r="EV10" t="inlineStr"/>
+      <c r="EW10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>2021 Q1→2021 Q2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.02709099394379777</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.01067387050191471</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.01945373076255752</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.01803774680762427</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.01342390218540856</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.001920047852569162</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.01517394518230297</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.0838248051523891</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0.2052556034488191</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.1706939118459889</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.07500633141940405</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0.02366905892394389</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.03505064192238194</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-0.03889993545965797</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0.0191923862852077</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-0.02954278534472632</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0.0161876518233699</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.008114690893096466</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.03417205233130982</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>-0.1698660906031861</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0.01115146803207345</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.161536066659437</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-0.03098279326046161</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.08133758442876449</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.1555447450087248</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-0.04310082364802614</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-0.0202027073175195</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-0.04141675798773203</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.009132720846352527</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-0.04979733786528939</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.002426428449654239</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-0.05765497305544631</v>
+      </c>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="n">
+        <v>-0.04356745537789042</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-0.01075359292355849</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-0.03074835897927741</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-0.1296504001277157</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.03338657056559935</v>
+      </c>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="inlineStr"/>
+      <c r="BN11" t="inlineStr"/>
+      <c r="BO11" t="inlineStr"/>
+      <c r="BP11" t="inlineStr"/>
+      <c r="BQ11" t="inlineStr"/>
+      <c r="BR11" t="inlineStr"/>
+      <c r="BS11" t="inlineStr"/>
+      <c r="BT11" t="inlineStr"/>
+      <c r="BU11" t="inlineStr"/>
+      <c r="BV11" t="inlineStr"/>
+      <c r="BW11" t="inlineStr"/>
+      <c r="BX11" t="inlineStr"/>
+      <c r="BY11" t="inlineStr"/>
+      <c r="BZ11" t="inlineStr"/>
+      <c r="CA11" t="inlineStr"/>
+      <c r="CB11" t="inlineStr"/>
+      <c r="CC11" t="inlineStr"/>
+      <c r="CD11" t="inlineStr"/>
+      <c r="CE11" t="inlineStr"/>
+      <c r="CF11" t="inlineStr"/>
+      <c r="CG11" t="inlineStr"/>
+      <c r="CH11" t="inlineStr"/>
+      <c r="CI11" t="inlineStr"/>
+      <c r="CJ11" t="inlineStr"/>
+      <c r="CK11" t="inlineStr"/>
+      <c r="CL11" t="inlineStr"/>
+      <c r="CM11" t="inlineStr"/>
+      <c r="CN11" t="inlineStr"/>
+      <c r="CO11" t="inlineStr"/>
+      <c r="CP11" t="inlineStr"/>
+      <c r="CQ11" t="inlineStr"/>
+      <c r="CR11" t="inlineStr"/>
+      <c r="CS11" t="inlineStr"/>
+      <c r="CT11" t="inlineStr"/>
+      <c r="CU11" t="inlineStr"/>
+      <c r="CV11" t="inlineStr"/>
+      <c r="CW11" t="inlineStr"/>
+      <c r="CX11" t="inlineStr"/>
+      <c r="CY11" t="inlineStr"/>
+      <c r="CZ11" t="inlineStr"/>
+      <c r="DA11" t="inlineStr"/>
+      <c r="DB11" t="inlineStr"/>
+      <c r="DC11" t="inlineStr"/>
+      <c r="DD11" t="inlineStr"/>
+      <c r="DE11" t="inlineStr"/>
+      <c r="DF11" t="inlineStr"/>
+      <c r="DG11" t="inlineStr"/>
+      <c r="DH11" t="inlineStr"/>
+      <c r="DI11" t="inlineStr"/>
+      <c r="DJ11" t="inlineStr"/>
+      <c r="DK11" t="inlineStr"/>
+      <c r="DL11" t="inlineStr"/>
+      <c r="DM11" t="inlineStr"/>
+      <c r="DN11" t="inlineStr"/>
+      <c r="DO11" t="inlineStr"/>
+      <c r="DP11" t="inlineStr"/>
+      <c r="DQ11" t="inlineStr"/>
+      <c r="DR11" t="inlineStr"/>
+      <c r="DS11" t="inlineStr"/>
+      <c r="DT11" t="inlineStr"/>
+      <c r="DU11" t="inlineStr"/>
+      <c r="DV11" t="inlineStr"/>
+      <c r="DW11" t="inlineStr"/>
+      <c r="DX11" t="inlineStr"/>
+      <c r="DY11" t="inlineStr"/>
+      <c r="DZ11" t="inlineStr"/>
+      <c r="EA11" t="inlineStr"/>
+      <c r="EB11" t="inlineStr"/>
+      <c r="EC11" t="inlineStr"/>
+      <c r="ED11" t="inlineStr"/>
+      <c r="EE11" t="inlineStr"/>
+      <c r="EF11" t="inlineStr"/>
+      <c r="EG11" t="inlineStr"/>
+      <c r="EH11" t="inlineStr"/>
+      <c r="EI11" t="inlineStr"/>
+      <c r="EJ11" t="inlineStr"/>
+      <c r="EK11" t="inlineStr"/>
+      <c r="EL11" t="inlineStr"/>
+      <c r="EM11" t="inlineStr"/>
+      <c r="EN11" t="inlineStr"/>
+      <c r="EO11" t="inlineStr"/>
+      <c r="EP11" t="inlineStr"/>
+      <c r="EQ11" t="inlineStr"/>
+      <c r="ER11" t="inlineStr"/>
+      <c r="ES11" t="inlineStr"/>
+      <c r="ET11" t="inlineStr"/>
+      <c r="EU11" t="inlineStr"/>
+      <c r="EV11" t="inlineStr"/>
+      <c r="EW11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2021 Q2→2021 Q3</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>-0.01610690976727369</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.0008661061017773974</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.006572543422105781</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.02086660300810195</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.02352790784557079</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.002456219150519523</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.01450745266678943</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0.05632951314177514</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-0.07873096825753034</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.139284045113973</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-0.07382144506471899</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.04227293448333658</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-0.01045093585309065</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0.05805796118784823</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0.03642987973249578</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-0.01112521117719822</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-0.05258249729195708</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0.008862649421908841</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-0.04333245081140014</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.02251223408472391</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.0177246474007049</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.2063858149940554</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-0.06312615764848317</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0.0237663073632044</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.0222206952856725</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0.007031351726864976</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-0.05007713784318657</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-0.1234126146453924</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-0.06064240337324289</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.1131574164378151</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-0.1312193899347518</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-0.05554859719022076</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.003390991666592846</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>-0.001265244993661874</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>-0.1387474631882313</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>-0.1134146781144167</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-0.1828591882660255</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-0.09588767206032234</v>
+      </c>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="n">
+        <v>-0.09947373971858475</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0.01033009526223605</v>
+      </c>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="inlineStr"/>
+      <c r="BN12" t="inlineStr"/>
+      <c r="BO12" t="inlineStr"/>
+      <c r="BP12" t="inlineStr"/>
+      <c r="BQ12" t="inlineStr"/>
+      <c r="BR12" t="inlineStr"/>
+      <c r="BS12" t="inlineStr"/>
+      <c r="BT12" t="inlineStr"/>
+      <c r="BU12" t="inlineStr"/>
+      <c r="BV12" t="inlineStr"/>
+      <c r="BW12" t="inlineStr"/>
+      <c r="BX12" t="inlineStr"/>
+      <c r="BY12" t="inlineStr"/>
+      <c r="BZ12" t="inlineStr"/>
+      <c r="CA12" t="inlineStr"/>
+      <c r="CB12" t="inlineStr"/>
+      <c r="CC12" t="inlineStr"/>
+      <c r="CD12" t="inlineStr"/>
+      <c r="CE12" t="inlineStr"/>
+      <c r="CF12" t="inlineStr"/>
+      <c r="CG12" t="inlineStr"/>
+      <c r="CH12" t="inlineStr"/>
+      <c r="CI12" t="inlineStr"/>
+      <c r="CJ12" t="inlineStr"/>
+      <c r="CK12" t="inlineStr"/>
+      <c r="CL12" t="inlineStr"/>
+      <c r="CM12" t="inlineStr"/>
+      <c r="CN12" t="inlineStr"/>
+      <c r="CO12" t="inlineStr"/>
+      <c r="CP12" t="inlineStr"/>
+      <c r="CQ12" t="inlineStr"/>
+      <c r="CR12" t="inlineStr"/>
+      <c r="CS12" t="inlineStr"/>
+      <c r="CT12" t="inlineStr"/>
+      <c r="CU12" t="inlineStr"/>
+      <c r="CV12" t="inlineStr"/>
+      <c r="CW12" t="inlineStr"/>
+      <c r="CX12" t="inlineStr"/>
+      <c r="CY12" t="inlineStr"/>
+      <c r="CZ12" t="inlineStr"/>
+      <c r="DA12" t="inlineStr"/>
+      <c r="DB12" t="inlineStr"/>
+      <c r="DC12" t="inlineStr"/>
+      <c r="DD12" t="inlineStr"/>
+      <c r="DE12" t="inlineStr"/>
+      <c r="DF12" t="inlineStr"/>
+      <c r="DG12" t="inlineStr"/>
+      <c r="DH12" t="inlineStr"/>
+      <c r="DI12" t="inlineStr"/>
+      <c r="DJ12" t="inlineStr"/>
+      <c r="DK12" t="inlineStr"/>
+      <c r="DL12" t="inlineStr"/>
+      <c r="DM12" t="inlineStr"/>
+      <c r="DN12" t="inlineStr"/>
+      <c r="DO12" t="inlineStr"/>
+      <c r="DP12" t="inlineStr"/>
+      <c r="DQ12" t="inlineStr"/>
+      <c r="DR12" t="inlineStr"/>
+      <c r="DS12" t="inlineStr"/>
+      <c r="DT12" t="inlineStr"/>
+      <c r="DU12" t="inlineStr"/>
+      <c r="DV12" t="inlineStr"/>
+      <c r="DW12" t="inlineStr"/>
+      <c r="DX12" t="inlineStr"/>
+      <c r="DY12" t="inlineStr"/>
+      <c r="DZ12" t="inlineStr"/>
+      <c r="EA12" t="inlineStr"/>
+      <c r="EB12" t="inlineStr"/>
+      <c r="EC12" t="inlineStr"/>
+      <c r="ED12" t="inlineStr"/>
+      <c r="EE12" t="inlineStr"/>
+      <c r="EF12" t="inlineStr"/>
+      <c r="EG12" t="inlineStr"/>
+      <c r="EH12" t="inlineStr"/>
+      <c r="EI12" t="inlineStr"/>
+      <c r="EJ12" t="inlineStr"/>
+      <c r="EK12" t="inlineStr"/>
+      <c r="EL12" t="inlineStr"/>
+      <c r="EM12" t="inlineStr"/>
+      <c r="EN12" t="inlineStr"/>
+      <c r="EO12" t="inlineStr"/>
+      <c r="EP12" t="inlineStr"/>
+      <c r="EQ12" t="inlineStr"/>
+      <c r="ER12" t="inlineStr"/>
+      <c r="ES12" t="inlineStr"/>
+      <c r="ET12" t="inlineStr"/>
+      <c r="EU12" t="inlineStr"/>
+      <c r="EV12" t="inlineStr"/>
+      <c r="EW12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>2021 Q3→2021 Q4</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-0.05113945488991778</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.0228480045245778</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.05043634841584765</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.04770141972269926</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.06681118013720599</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.10306531618909</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.05785065686429292</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0.07690689612151758</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-0.03102009699491859</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.1012816282815061</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0.07700851709324841</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-0.1018300874975546</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-0.1193776500956805</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-0.08244204027689328</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.08273290836368563</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0.08110484266452023</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-0.01869268588611561</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0.08429370632250865</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.05981970642324086</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>-0.07564775351188668</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-0.1051547153375676</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.02725190720168413</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-0.03762093451364912</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0.06985099036682474</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-0.134907715434859</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-0.1998022531628711</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-0.2319199921424095</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0.09639982318557738</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-0.3652918716239251</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-0.2012404596068436</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-0.08779545760915752</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-0.01922858562694785</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>-0.05831156564804996</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>-0.08168716626124795</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-0.06087923671278173</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>-0.08852084985628927</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-0.08711913754577871</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-0.09639893749642248</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-0.1030147511096704</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-0.04380827953634636</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0.03446720649836355</v>
+      </c>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="n">
+        <v>-0.03080197879141977</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>-0.009183702247860026</v>
+      </c>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="inlineStr"/>
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="inlineStr"/>
+      <c r="BO13" t="inlineStr"/>
+      <c r="BP13" t="inlineStr"/>
+      <c r="BQ13" t="inlineStr"/>
+      <c r="BR13" t="inlineStr"/>
+      <c r="BS13" t="inlineStr"/>
+      <c r="BT13" t="inlineStr"/>
+      <c r="BU13" t="inlineStr"/>
+      <c r="BV13" t="inlineStr"/>
+      <c r="BW13" t="inlineStr"/>
+      <c r="BX13" t="inlineStr"/>
+      <c r="BY13" t="inlineStr"/>
+      <c r="BZ13" t="inlineStr"/>
+      <c r="CA13" t="inlineStr"/>
+      <c r="CB13" t="inlineStr"/>
+      <c r="CC13" t="inlineStr"/>
+      <c r="CD13" t="inlineStr"/>
+      <c r="CE13" t="inlineStr"/>
+      <c r="CF13" t="inlineStr"/>
+      <c r="CG13" t="inlineStr"/>
+      <c r="CH13" t="inlineStr"/>
+      <c r="CI13" t="inlineStr"/>
+      <c r="CJ13" t="inlineStr"/>
+      <c r="CK13" t="inlineStr"/>
+      <c r="CL13" t="inlineStr"/>
+      <c r="CM13" t="inlineStr"/>
+      <c r="CN13" t="inlineStr"/>
+      <c r="CO13" t="inlineStr"/>
+      <c r="CP13" t="inlineStr"/>
+      <c r="CQ13" t="inlineStr"/>
+      <c r="CR13" t="inlineStr"/>
+      <c r="CS13" t="inlineStr"/>
+      <c r="CT13" t="inlineStr"/>
+      <c r="CU13" t="inlineStr"/>
+      <c r="CV13" t="inlineStr"/>
+      <c r="CW13" t="inlineStr"/>
+      <c r="CX13" t="inlineStr"/>
+      <c r="CY13" t="inlineStr"/>
+      <c r="CZ13" t="inlineStr"/>
+      <c r="DA13" t="inlineStr"/>
+      <c r="DB13" t="inlineStr"/>
+      <c r="DC13" t="inlineStr"/>
+      <c r="DD13" t="inlineStr"/>
+      <c r="DE13" t="inlineStr"/>
+      <c r="DF13" t="inlineStr"/>
+      <c r="DG13" t="inlineStr"/>
+      <c r="DH13" t="inlineStr"/>
+      <c r="DI13" t="inlineStr"/>
+      <c r="DJ13" t="inlineStr"/>
+      <c r="DK13" t="inlineStr"/>
+      <c r="DL13" t="inlineStr"/>
+      <c r="DM13" t="inlineStr"/>
+      <c r="DN13" t="inlineStr"/>
+      <c r="DO13" t="inlineStr"/>
+      <c r="DP13" t="inlineStr"/>
+      <c r="DQ13" t="inlineStr"/>
+      <c r="DR13" t="inlineStr"/>
+      <c r="DS13" t="inlineStr"/>
+      <c r="DT13" t="inlineStr"/>
+      <c r="DU13" t="inlineStr"/>
+      <c r="DV13" t="inlineStr"/>
+      <c r="DW13" t="inlineStr"/>
+      <c r="DX13" t="inlineStr"/>
+      <c r="DY13" t="inlineStr"/>
+      <c r="DZ13" t="inlineStr"/>
+      <c r="EA13" t="inlineStr"/>
+      <c r="EB13" t="inlineStr"/>
+      <c r="EC13" t="inlineStr"/>
+      <c r="ED13" t="inlineStr"/>
+      <c r="EE13" t="inlineStr"/>
+      <c r="EF13" t="inlineStr"/>
+      <c r="EG13" t="inlineStr"/>
+      <c r="EH13" t="inlineStr"/>
+      <c r="EI13" t="inlineStr"/>
+      <c r="EJ13" t="inlineStr"/>
+      <c r="EK13" t="inlineStr"/>
+      <c r="EL13" t="inlineStr"/>
+      <c r="EM13" t="inlineStr"/>
+      <c r="EN13" t="inlineStr"/>
+      <c r="EO13" t="inlineStr"/>
+      <c r="EP13" t="inlineStr"/>
+      <c r="EQ13" t="inlineStr"/>
+      <c r="ER13" t="inlineStr"/>
+      <c r="ES13" t="inlineStr"/>
+      <c r="ET13" t="inlineStr"/>
+      <c r="EU13" t="inlineStr"/>
+      <c r="EV13" t="inlineStr"/>
+      <c r="EW13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>2021 Q4→2022 Q1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>-0.2049233390281353</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.2298404955020219</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.2204146053780374</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.1733925993123835</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.1888234464181382</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.2083571610281822</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.1735937014628348</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0.1842469299483342</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-0.0270675241379168</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.1075767860773258</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-0.1414242435348392</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-0.1561890482906998</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-0.2002469400879932</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-0.1842846423618045</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.1936948762281387</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-0.1912270412496264</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-0.1920055550021669</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-0.2334623843676003</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0.1779754924481853</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>-0.02804247125854875</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.1749838166883313</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.02892116666017941</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-0.08987297155793339</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0.02768794285354748</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-0.2575085869725831</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-0.1887543001737502</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-0.1443138771025323</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0.1808729983803943</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-0.132311667413183</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-0.1580409420869975</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-0.08464612364946422</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-0.1585622153865813</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-0.1594092370807259</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>-0.1592027027443716</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>-0.1358422822985972</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>-0.1118550040615292</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.02135944876761986</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-0.02313801822242922</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-0.1018673430728327</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-0.1534819329230288</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-0.07106746745946158</v>
+      </c>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="n">
+        <v>-0.06359456039800193</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0.09640440833848807</v>
+      </c>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="n">
+        <v>-0.06765209102271097</v>
+      </c>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="n">
+        <v>-0.005321828147822671</v>
+      </c>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="n">
+        <v>0.007946910919810257</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>-0.00404072024298241</v>
+      </c>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr"/>
+      <c r="BI14" t="inlineStr"/>
+      <c r="BJ14" t="inlineStr"/>
+      <c r="BK14" t="inlineStr"/>
+      <c r="BL14" t="inlineStr"/>
+      <c r="BM14" t="inlineStr"/>
+      <c r="BN14" t="inlineStr"/>
+      <c r="BO14" t="inlineStr"/>
+      <c r="BP14" t="inlineStr"/>
+      <c r="BQ14" t="inlineStr"/>
+      <c r="BR14" t="inlineStr"/>
+      <c r="BS14" t="inlineStr"/>
+      <c r="BT14" t="inlineStr"/>
+      <c r="BU14" t="inlineStr"/>
+      <c r="BV14" t="inlineStr"/>
+      <c r="BW14" t="inlineStr"/>
+      <c r="BX14" t="inlineStr"/>
+      <c r="BY14" t="inlineStr"/>
+      <c r="BZ14" t="inlineStr"/>
+      <c r="CA14" t="inlineStr"/>
+      <c r="CB14" t="inlineStr"/>
+      <c r="CC14" t="inlineStr"/>
+      <c r="CD14" t="inlineStr"/>
+      <c r="CE14" t="inlineStr"/>
+      <c r="CF14" t="inlineStr"/>
+      <c r="CG14" t="inlineStr"/>
+      <c r="CH14" t="inlineStr"/>
+      <c r="CI14" t="inlineStr"/>
+      <c r="CJ14" t="inlineStr"/>
+      <c r="CK14" t="inlineStr"/>
+      <c r="CL14" t="inlineStr"/>
+      <c r="CM14" t="inlineStr"/>
+      <c r="CN14" t="inlineStr"/>
+      <c r="CO14" t="inlineStr"/>
+      <c r="CP14" t="inlineStr"/>
+      <c r="CQ14" t="inlineStr"/>
+      <c r="CR14" t="inlineStr"/>
+      <c r="CS14" t="inlineStr"/>
+      <c r="CT14" t="inlineStr"/>
+      <c r="CU14" t="inlineStr"/>
+      <c r="CV14" t="inlineStr"/>
+      <c r="CW14" t="inlineStr"/>
+      <c r="CX14" t="inlineStr"/>
+      <c r="CY14" t="inlineStr"/>
+      <c r="CZ14" t="inlineStr"/>
+      <c r="DA14" t="inlineStr"/>
+      <c r="DB14" t="inlineStr"/>
+      <c r="DC14" t="inlineStr"/>
+      <c r="DD14" t="inlineStr"/>
+      <c r="DE14" t="inlineStr"/>
+      <c r="DF14" t="inlineStr"/>
+      <c r="DG14" t="inlineStr"/>
+      <c r="DH14" t="inlineStr"/>
+      <c r="DI14" t="inlineStr"/>
+      <c r="DJ14" t="inlineStr"/>
+      <c r="DK14" t="inlineStr"/>
+      <c r="DL14" t="inlineStr"/>
+      <c r="DM14" t="inlineStr"/>
+      <c r="DN14" t="inlineStr"/>
+      <c r="DO14" t="inlineStr"/>
+      <c r="DP14" t="inlineStr"/>
+      <c r="DQ14" t="inlineStr"/>
+      <c r="DR14" t="inlineStr"/>
+      <c r="DS14" t="inlineStr"/>
+      <c r="DT14" t="inlineStr"/>
+      <c r="DU14" t="inlineStr"/>
+      <c r="DV14" t="inlineStr"/>
+      <c r="DW14" t="inlineStr"/>
+      <c r="DX14" t="inlineStr"/>
+      <c r="DY14" t="inlineStr"/>
+      <c r="DZ14" t="inlineStr"/>
+      <c r="EA14" t="inlineStr"/>
+      <c r="EB14" t="inlineStr"/>
+      <c r="EC14" t="inlineStr"/>
+      <c r="ED14" t="inlineStr"/>
+      <c r="EE14" t="inlineStr"/>
+      <c r="EF14" t="inlineStr"/>
+      <c r="EG14" t="inlineStr"/>
+      <c r="EH14" t="inlineStr"/>
+      <c r="EI14" t="inlineStr"/>
+      <c r="EJ14" t="inlineStr"/>
+      <c r="EK14" t="inlineStr"/>
+      <c r="EL14" t="inlineStr"/>
+      <c r="EM14" t="inlineStr"/>
+      <c r="EN14" t="inlineStr"/>
+      <c r="EO14" t="inlineStr"/>
+      <c r="EP14" t="inlineStr"/>
+      <c r="EQ14" t="inlineStr"/>
+      <c r="ER14" t="inlineStr"/>
+      <c r="ES14" t="inlineStr"/>
+      <c r="ET14" t="inlineStr"/>
+      <c r="EU14" t="inlineStr"/>
+      <c r="EV14" t="inlineStr"/>
+      <c r="EW14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>2022 Q1→2022 Q2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>-0.09936014469261334</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.04562227246619699</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.01561596061388748</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.1546061735447655</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.09009575463942276</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.09217993090867438</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.1330910154764426</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-0.114066546111828</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-0.1662544485205268</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.2562973255199292</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-0.1159993222944617</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-0.09343389015181813</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0.03034305017148853</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-0.04547747157371429</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0.02430590558094625</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.06135417609115201</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-0.02910617620264766</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.05005698056721997</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.01929544805967076</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>-0.1582420775626732</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.05603736555008609</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.03739448539647938</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.02710767348001308</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-0.1729301605269367</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-0.03005201054737761</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-0.06770229798661287</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-0.0766842040341098</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-0.06386629915678999</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-0.03821416872297512</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-0.06319328933149571</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>-0.08599703374951773</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>-0.1327996602888195</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-0.0749336831306282</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>-0.09805807204701988</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>-0.05051153802329633</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>-0.1087665745590369</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-0.04436066263493998</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0.06106945758330085</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-0.1302361750266696</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-0.09641670326077545</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-0.1648738826324561</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0.003536262042749705</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>-0.02035275333382192</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>-0.1073094873745015</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>-0.1043665404181224</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>-0.09258300844329259</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>-0.03556699229244931</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-0.02706448309762699</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>-0.007782240051907863</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>-0.04309128148040209</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>-0.1723591516355114</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>-0.2284744160026113</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>-0.1151882886014972</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>-0.06987080778067067</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>-0.1690970297673129</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>-0.1855926359452518</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>-0.04440562928633973</v>
+      </c>
+      <c r="BH15" t="inlineStr"/>
+      <c r="BI15" t="n">
+        <v>-0.3276521478280126</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>-0.05362573040568996</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>-0.09753347166377768</v>
+      </c>
+      <c r="BL15" t="inlineStr"/>
+      <c r="BM15" t="n">
+        <v>-0.1268355437635416</v>
+      </c>
+      <c r="BN15" t="inlineStr"/>
+      <c r="BO15" t="inlineStr"/>
+      <c r="BP15" t="inlineStr"/>
+      <c r="BQ15" t="inlineStr"/>
+      <c r="BR15" t="inlineStr"/>
+      <c r="BS15" t="inlineStr"/>
+      <c r="BT15" t="inlineStr"/>
+      <c r="BU15" t="inlineStr"/>
+      <c r="BV15" t="inlineStr"/>
+      <c r="BW15" t="inlineStr"/>
+      <c r="BX15" t="inlineStr"/>
+      <c r="BY15" t="inlineStr"/>
+      <c r="BZ15" t="inlineStr"/>
+      <c r="CA15" t="inlineStr"/>
+      <c r="CB15" t="inlineStr"/>
+      <c r="CC15" t="inlineStr"/>
+      <c r="CD15" t="inlineStr"/>
+      <c r="CE15" t="inlineStr"/>
+      <c r="CF15" t="inlineStr"/>
+      <c r="CG15" t="inlineStr"/>
+      <c r="CH15" t="inlineStr"/>
+      <c r="CI15" t="inlineStr"/>
+      <c r="CJ15" t="inlineStr"/>
+      <c r="CK15" t="inlineStr"/>
+      <c r="CL15" t="inlineStr"/>
+      <c r="CM15" t="inlineStr"/>
+      <c r="CN15" t="inlineStr"/>
+      <c r="CO15" t="inlineStr"/>
+      <c r="CP15" t="inlineStr"/>
+      <c r="CQ15" t="inlineStr"/>
+      <c r="CR15" t="inlineStr"/>
+      <c r="CS15" t="inlineStr"/>
+      <c r="CT15" t="inlineStr"/>
+      <c r="CU15" t="inlineStr"/>
+      <c r="CV15" t="inlineStr"/>
+      <c r="CW15" t="inlineStr"/>
+      <c r="CX15" t="inlineStr"/>
+      <c r="CY15" t="inlineStr"/>
+      <c r="CZ15" t="inlineStr"/>
+      <c r="DA15" t="inlineStr"/>
+      <c r="DB15" t="inlineStr"/>
+      <c r="DC15" t="inlineStr"/>
+      <c r="DD15" t="inlineStr"/>
+      <c r="DE15" t="inlineStr"/>
+      <c r="DF15" t="inlineStr"/>
+      <c r="DG15" t="inlineStr"/>
+      <c r="DH15" t="inlineStr"/>
+      <c r="DI15" t="inlineStr"/>
+      <c r="DJ15" t="inlineStr"/>
+      <c r="DK15" t="inlineStr"/>
+      <c r="DL15" t="inlineStr"/>
+      <c r="DM15" t="inlineStr"/>
+      <c r="DN15" t="inlineStr"/>
+      <c r="DO15" t="inlineStr"/>
+      <c r="DP15" t="inlineStr"/>
+      <c r="DQ15" t="inlineStr"/>
+      <c r="DR15" t="inlineStr"/>
+      <c r="DS15" t="inlineStr"/>
+      <c r="DT15" t="inlineStr"/>
+      <c r="DU15" t="inlineStr"/>
+      <c r="DV15" t="inlineStr"/>
+      <c r="DW15" t="inlineStr"/>
+      <c r="DX15" t="inlineStr"/>
+      <c r="DY15" t="inlineStr"/>
+      <c r="DZ15" t="inlineStr"/>
+      <c r="EA15" t="inlineStr"/>
+      <c r="EB15" t="inlineStr"/>
+      <c r="EC15" t="inlineStr"/>
+      <c r="ED15" t="inlineStr"/>
+      <c r="EE15" t="inlineStr"/>
+      <c r="EF15" t="inlineStr"/>
+      <c r="EG15" t="inlineStr"/>
+      <c r="EH15" t="inlineStr"/>
+      <c r="EI15" t="inlineStr"/>
+      <c r="EJ15" t="inlineStr"/>
+      <c r="EK15" t="inlineStr"/>
+      <c r="EL15" t="inlineStr"/>
+      <c r="EM15" t="inlineStr"/>
+      <c r="EN15" t="inlineStr"/>
+      <c r="EO15" t="inlineStr"/>
+      <c r="EP15" t="inlineStr"/>
+      <c r="EQ15" t="inlineStr"/>
+      <c r="ER15" t="inlineStr"/>
+      <c r="ES15" t="inlineStr"/>
+      <c r="ET15" t="inlineStr"/>
+      <c r="EU15" t="inlineStr"/>
+      <c r="EV15" t="inlineStr"/>
+      <c r="EW15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>2022 Q2→2022 Q3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.04641337171882753</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.002251306301113587</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.03858010662962919</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.006484859651197716</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.04042667440023795</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.01334807490949697</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.005834623311613107</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.07202966034845382</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-0.1888843367064785</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0.1023443442558687</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-0.01338361297246404</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-0.028669393659424</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-0.009107861229013636</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-0.06006455382679654</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.0003985916481399343</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.02582439990077923</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-0.02844491845509989</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.09062522541546958</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.005954263909211832</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>-0.1147809063020588</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.1143233133265502</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.01440022107931771</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-0.2244205654542757</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-0.2883943231941419</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-0.00557476940909396</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-0.02415870892794469</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-0.07154582139782129</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-0.05646950867510458</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-0.04503627118789222</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-0.05063751374891012</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-0.01323459438173824</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>-0.03299595456010707</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-0.05099337705930562</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>-0.0005718480894598699</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>-0.04306279525103474</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.007798844665384053</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>-0.1317004235621182</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>-0.1574543766429271</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>-0.2920998701989168</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>-0.151139480745452</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>-0.2033616158696638</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>-0.1001634377378293</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>-0.07601303702580786</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>-0.1035821050877352</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>-0.07162619008161109</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>-0.006912042142967145</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>-0.008599900476837341</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>-0.06130155952016381</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>-0.04076952640399334</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>-0.02896666401863968</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>-0.1764029308590302</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>-0.07941930714118683</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>-0.06877081271641838</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>-0.1519165207623985</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>-0.0505943637053381</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>-0.08921111829806971</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>-0.07882896862394162</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0.01474296522425877</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>-0.2327123564292002</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>-0.3477213388416898</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>-0.2514452315484679</v>
+      </c>
+      <c r="BL16" t="inlineStr"/>
+      <c r="BM16" t="n">
+        <v>-0.1516817782311755</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>-0.120625877939311</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>-0.07188503943255675</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>-0.1607498445854914</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>-0.001445374151789025</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>-0.1571251586075846</v>
+      </c>
+      <c r="BS16" t="inlineStr"/>
+      <c r="BT16" t="inlineStr"/>
+      <c r="BU16" t="inlineStr"/>
+      <c r="BV16" t="inlineStr"/>
+      <c r="BW16" t="inlineStr"/>
+      <c r="BX16" t="inlineStr"/>
+      <c r="BY16" t="inlineStr"/>
+      <c r="BZ16" t="inlineStr"/>
+      <c r="CA16" t="inlineStr"/>
+      <c r="CB16" t="inlineStr"/>
+      <c r="CC16" t="inlineStr"/>
+      <c r="CD16" t="inlineStr"/>
+      <c r="CE16" t="inlineStr"/>
+      <c r="CF16" t="inlineStr"/>
+      <c r="CG16" t="inlineStr"/>
+      <c r="CH16" t="inlineStr"/>
+      <c r="CI16" t="inlineStr"/>
+      <c r="CJ16" t="inlineStr"/>
+      <c r="CK16" t="inlineStr"/>
+      <c r="CL16" t="inlineStr"/>
+      <c r="CM16" t="inlineStr"/>
+      <c r="CN16" t="inlineStr"/>
+      <c r="CO16" t="inlineStr"/>
+      <c r="CP16" t="inlineStr"/>
+      <c r="CQ16" t="inlineStr"/>
+      <c r="CR16" t="inlineStr"/>
+      <c r="CS16" t="inlineStr"/>
+      <c r="CT16" t="inlineStr"/>
+      <c r="CU16" t="inlineStr"/>
+      <c r="CV16" t="inlineStr"/>
+      <c r="CW16" t="inlineStr"/>
+      <c r="CX16" t="inlineStr"/>
+      <c r="CY16" t="inlineStr"/>
+      <c r="CZ16" t="inlineStr"/>
+      <c r="DA16" t="inlineStr"/>
+      <c r="DB16" t="inlineStr"/>
+      <c r="DC16" t="inlineStr"/>
+      <c r="DD16" t="inlineStr"/>
+      <c r="DE16" t="inlineStr"/>
+      <c r="DF16" t="inlineStr"/>
+      <c r="DG16" t="inlineStr"/>
+      <c r="DH16" t="inlineStr"/>
+      <c r="DI16" t="inlineStr"/>
+      <c r="DJ16" t="inlineStr"/>
+      <c r="DK16" t="inlineStr"/>
+      <c r="DL16" t="inlineStr"/>
+      <c r="DM16" t="inlineStr"/>
+      <c r="DN16" t="inlineStr"/>
+      <c r="DO16" t="inlineStr"/>
+      <c r="DP16" t="inlineStr"/>
+      <c r="DQ16" t="inlineStr"/>
+      <c r="DR16" t="inlineStr"/>
+      <c r="DS16" t="inlineStr"/>
+      <c r="DT16" t="inlineStr"/>
+      <c r="DU16" t="inlineStr"/>
+      <c r="DV16" t="inlineStr"/>
+      <c r="DW16" t="inlineStr"/>
+      <c r="DX16" t="inlineStr"/>
+      <c r="DY16" t="inlineStr"/>
+      <c r="DZ16" t="inlineStr"/>
+      <c r="EA16" t="inlineStr"/>
+      <c r="EB16" t="inlineStr"/>
+      <c r="EC16" t="inlineStr"/>
+      <c r="ED16" t="inlineStr"/>
+      <c r="EE16" t="inlineStr"/>
+      <c r="EF16" t="inlineStr"/>
+      <c r="EG16" t="inlineStr"/>
+      <c r="EH16" t="inlineStr"/>
+      <c r="EI16" t="inlineStr"/>
+      <c r="EJ16" t="inlineStr"/>
+      <c r="EK16" t="inlineStr"/>
+      <c r="EL16" t="inlineStr"/>
+      <c r="EM16" t="inlineStr"/>
+      <c r="EN16" t="inlineStr"/>
+      <c r="EO16" t="inlineStr"/>
+      <c r="EP16" t="inlineStr"/>
+      <c r="EQ16" t="inlineStr"/>
+      <c r="ER16" t="inlineStr"/>
+      <c r="ES16" t="inlineStr"/>
+      <c r="ET16" t="inlineStr"/>
+      <c r="EU16" t="inlineStr"/>
+      <c r="EV16" t="inlineStr"/>
+      <c r="EW16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>2022 Q3→2022 Q4</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>-0.04634820603505307</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.1179049645719772</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.01419768200250981</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.04847335757720472</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0.07803750656337982</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.04635872831358689</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.07041272606948557</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-0.08227760927410976</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-0.04995133189097078</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.01375298900806854</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-0.08055232212863217</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-0.1259652622266714</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-0.1793807592052845</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-0.0861802562294347</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-0.2632622688887603</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-0.2525144316356185</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-0.2034141814079025</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0.2848809215356773</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-0.2479367391855085</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>-0.005352491104329005</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-0.1803129136059081</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.02092452140103429</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-0.08109176148511299</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-0.1536428195240918</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-0.2813505358705957</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-0.2390146339843628</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-0.2495917453474563</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-0.2437132827413704</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-0.2150647131385739</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-0.2472726726571182</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>-0.1678568117169039</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-0.1503208893392216</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>-0.1746956573992131</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>-0.2101112242407766</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>-0.09703345460562218</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>-0.09117316665530861</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.05216301000346935</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>-0.1312668320151475</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>-0.08111481953707678</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>-0.1882904683290834</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>-0.2296601360852382</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0.00129118910614956</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>-0.09980053310595149</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>-0.138972551743703</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0.03333599509327634</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>-0.1289296077236362</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>-0.08708841653762356</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>-0.1236132849971323</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>-0.118331945548535</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>-0.07995467183727456</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>-0.1674336254548017</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>-0.1432797279293228</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>-0.2333671440840961</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>-0.2326039529833652</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>-0.2089684275499</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>-0.136182504148219</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>-0.0572915031102692</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>-0.1452745799919466</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0.1153658548029268</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0.03870471246723373</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>-0.1656102514507234</v>
+      </c>
+      <c r="BL17" t="inlineStr"/>
+      <c r="BM17" t="n">
+        <v>-0.189139042474225</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>-0.3174987781460183</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>-0.125721400243294</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>0.1467794180295101</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>-0.1264355957328673</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>-0.2605544869689203</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>-0.1237262363188565</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>-0.2823724388201265</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>-0.01985686605520964</v>
+      </c>
+      <c r="BV17" t="inlineStr"/>
+      <c r="BW17" t="inlineStr"/>
+      <c r="BX17" t="n">
+        <v>0.1302280703176155</v>
+      </c>
+      <c r="BY17" t="inlineStr"/>
+      <c r="BZ17" t="inlineStr"/>
+      <c r="CA17" t="inlineStr"/>
+      <c r="CB17" t="inlineStr"/>
+      <c r="CC17" t="inlineStr"/>
+      <c r="CD17" t="inlineStr"/>
+      <c r="CE17" t="inlineStr"/>
+      <c r="CF17" t="inlineStr"/>
+      <c r="CG17" t="inlineStr"/>
+      <c r="CH17" t="inlineStr"/>
+      <c r="CI17" t="inlineStr"/>
+      <c r="CJ17" t="inlineStr"/>
+      <c r="CK17" t="inlineStr"/>
+      <c r="CL17" t="inlineStr"/>
+      <c r="CM17" t="inlineStr"/>
+      <c r="CN17" t="inlineStr"/>
+      <c r="CO17" t="inlineStr"/>
+      <c r="CP17" t="inlineStr"/>
+      <c r="CQ17" t="inlineStr"/>
+      <c r="CR17" t="inlineStr"/>
+      <c r="CS17" t="inlineStr"/>
+      <c r="CT17" t="inlineStr"/>
+      <c r="CU17" t="inlineStr"/>
+      <c r="CV17" t="inlineStr"/>
+      <c r="CW17" t="inlineStr"/>
+      <c r="CX17" t="inlineStr"/>
+      <c r="CY17" t="inlineStr"/>
+      <c r="CZ17" t="inlineStr"/>
+      <c r="DA17" t="inlineStr"/>
+      <c r="DB17" t="inlineStr"/>
+      <c r="DC17" t="inlineStr"/>
+      <c r="DD17" t="inlineStr"/>
+      <c r="DE17" t="inlineStr"/>
+      <c r="DF17" t="inlineStr"/>
+      <c r="DG17" t="inlineStr"/>
+      <c r="DH17" t="inlineStr"/>
+      <c r="DI17" t="inlineStr"/>
+      <c r="DJ17" t="inlineStr"/>
+      <c r="DK17" t="inlineStr"/>
+      <c r="DL17" t="inlineStr"/>
+      <c r="DM17" t="inlineStr"/>
+      <c r="DN17" t="inlineStr"/>
+      <c r="DO17" t="inlineStr"/>
+      <c r="DP17" t="inlineStr"/>
+      <c r="DQ17" t="inlineStr"/>
+      <c r="DR17" t="inlineStr"/>
+      <c r="DS17" t="inlineStr"/>
+      <c r="DT17" t="inlineStr"/>
+      <c r="DU17" t="inlineStr"/>
+      <c r="DV17" t="inlineStr"/>
+      <c r="DW17" t="inlineStr"/>
+      <c r="DX17" t="inlineStr"/>
+      <c r="DY17" t="inlineStr"/>
+      <c r="DZ17" t="inlineStr"/>
+      <c r="EA17" t="inlineStr"/>
+      <c r="EB17" t="inlineStr"/>
+      <c r="EC17" t="inlineStr"/>
+      <c r="ED17" t="inlineStr"/>
+      <c r="EE17" t="inlineStr"/>
+      <c r="EF17" t="inlineStr"/>
+      <c r="EG17" t="inlineStr"/>
+      <c r="EH17" t="inlineStr"/>
+      <c r="EI17" t="inlineStr"/>
+      <c r="EJ17" t="inlineStr"/>
+      <c r="EK17" t="inlineStr"/>
+      <c r="EL17" t="inlineStr"/>
+      <c r="EM17" t="inlineStr"/>
+      <c r="EN17" t="inlineStr"/>
+      <c r="EO17" t="inlineStr"/>
+      <c r="EP17" t="inlineStr"/>
+      <c r="EQ17" t="inlineStr"/>
+      <c r="ER17" t="inlineStr"/>
+      <c r="ES17" t="inlineStr"/>
+      <c r="ET17" t="inlineStr"/>
+      <c r="EU17" t="inlineStr"/>
+      <c r="EV17" t="inlineStr"/>
+      <c r="EW17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>2022 Q4→2023 Q1</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>-0.1090890212502762</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.08403391603440902</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.1445682191410196</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.05126995471360463</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.09598349906479342</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.04787628057823667</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.09186504690600206</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-0.1105377931512335</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0.0210276375676095</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0.0450269196079125</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.05264797755507811</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-0.04039729638736933</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-0.07106267098030283</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-0.05742555110755898</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.04208413870605643</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-0.05253335939528547</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-0.08888305242866412</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-0.07956810769371625</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.08516047746612809</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>-0.04856201910031199</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-0.1119804414610446</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.07106941245725906</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.06351522479218108</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-0.08754442716143185</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-0.05460597742588025</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-0.02976671076254434</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-0.03089158952873294</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-0.02727068222265494</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-0.03459491277123483</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-0.0426460932239463</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>-0.1501153098844181</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>-0.120522257190081</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>-0.1271738809967911</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>-0.112494333136075</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>-0.1567986232255079</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>-0.2094447069560479</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>-0.06916346172960353</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>-0.0592101174730848</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>-0.003853478213758699</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>-0.2023666691949746</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>-0.09560633318461687</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>-0.0002581044821265976</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>-0.132546655961983</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>-0.05896424963637426</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>-0.1552236514023342</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>-0.06631817137741969</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>-0.1495741751655411</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>-0.0613046712319063</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>-0.0944954581463211</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>-0.09391715504296982</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>-0.0895997064054832</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>-0.02504541599964671</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>-0.0530842141214567</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>-0.04579589364397485</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>-0.03898967186308688</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>-0.08907477378704165</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>-0.002398640727596657</v>
+      </c>
+      <c r="BH18" t="inlineStr"/>
+      <c r="BI18" t="n">
+        <v>-0.004986263185301709</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>-0.1903038773988239</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>-0.03284811353957195</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>-0.006941781718119877</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>0.08881539874813349</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>-0.02522516669945318</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>-0.05196328518139026</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>-0.2971300317186261</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>0.02352095456041337</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>-0.3380891894436191</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>0.07162412296786247</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>-0.04725501185165548</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>0.009371842083583992</v>
+      </c>
+      <c r="BV18" t="inlineStr"/>
+      <c r="BW18" t="n">
+        <v>0.107161110875035</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>-0.1191448334396332</v>
+      </c>
+      <c r="BY18" t="inlineStr"/>
+      <c r="BZ18" t="n">
+        <v>0.2757781646527713</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>-0.01940517291440003</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>0.009215132612987453</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>-0.1143236764497573</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>-0.117652458484037</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>-0.1658666453950532</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>-0.1070181453252941</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>-0.1571228485944278</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>-0.06782672191979788</v>
+      </c>
+      <c r="CI18" t="inlineStr"/>
+      <c r="CJ18" t="n">
+        <v>-0.1000976621676353</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>-0.08737068711805662</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>-0.1470013272808677</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>-0.09403805890763195</v>
+      </c>
+      <c r="CN18" t="inlineStr"/>
+      <c r="CO18" t="inlineStr"/>
+      <c r="CP18" t="inlineStr"/>
+      <c r="CQ18" t="inlineStr"/>
+      <c r="CR18" t="inlineStr"/>
+      <c r="CS18" t="inlineStr"/>
+      <c r="CT18" t="inlineStr"/>
+      <c r="CU18" t="inlineStr"/>
+      <c r="CV18" t="inlineStr"/>
+      <c r="CW18" t="inlineStr"/>
+      <c r="CX18" t="inlineStr"/>
+      <c r="CY18" t="inlineStr"/>
+      <c r="CZ18" t="inlineStr"/>
+      <c r="DA18" t="inlineStr"/>
+      <c r="DB18" t="inlineStr"/>
+      <c r="DC18" t="inlineStr"/>
+      <c r="DD18" t="inlineStr"/>
+      <c r="DE18" t="inlineStr"/>
+      <c r="DF18" t="inlineStr"/>
+      <c r="DG18" t="inlineStr"/>
+      <c r="DH18" t="inlineStr"/>
+      <c r="DI18" t="inlineStr"/>
+      <c r="DJ18" t="inlineStr"/>
+      <c r="DK18" t="inlineStr"/>
+      <c r="DL18" t="inlineStr"/>
+      <c r="DM18" t="inlineStr"/>
+      <c r="DN18" t="inlineStr"/>
+      <c r="DO18" t="inlineStr"/>
+      <c r="DP18" t="inlineStr"/>
+      <c r="DQ18" t="inlineStr"/>
+      <c r="DR18" t="inlineStr"/>
+      <c r="DS18" t="inlineStr"/>
+      <c r="DT18" t="inlineStr"/>
+      <c r="DU18" t="inlineStr"/>
+      <c r="DV18" t="inlineStr"/>
+      <c r="DW18" t="inlineStr"/>
+      <c r="DX18" t="inlineStr"/>
+      <c r="DY18" t="inlineStr"/>
+      <c r="DZ18" t="inlineStr"/>
+      <c r="EA18" t="inlineStr"/>
+      <c r="EB18" t="inlineStr"/>
+      <c r="EC18" t="inlineStr"/>
+      <c r="ED18" t="inlineStr"/>
+      <c r="EE18" t="inlineStr"/>
+      <c r="EF18" t="inlineStr"/>
+      <c r="EG18" t="inlineStr"/>
+      <c r="EH18" t="inlineStr"/>
+      <c r="EI18" t="inlineStr"/>
+      <c r="EJ18" t="inlineStr"/>
+      <c r="EK18" t="inlineStr"/>
+      <c r="EL18" t="inlineStr"/>
+      <c r="EM18" t="inlineStr"/>
+      <c r="EN18" t="inlineStr"/>
+      <c r="EO18" t="inlineStr"/>
+      <c r="EP18" t="inlineStr"/>
+      <c r="EQ18" t="inlineStr"/>
+      <c r="ER18" t="inlineStr"/>
+      <c r="ES18" t="inlineStr"/>
+      <c r="ET18" t="inlineStr"/>
+      <c r="EU18" t="inlineStr"/>
+      <c r="EV18" t="inlineStr"/>
+      <c r="EW18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>2023 Q1→2023 Q2</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.04792461804237824</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.0359187465386448</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.005693408614608764</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.04468512935446523</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.07605081920170598</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.05017401306613056</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.03437745052885255</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.05460074285361838</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-0.008340405918513483</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.01266276848528936</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-0.01790294977580054</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.01330077723550627</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.0324191018513611</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.03762190912326169</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.03509664806263579</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.0003427657420163044</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.04609064479657743</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.005987245133922237</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.07982135075472563</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.3065222820806808</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-0.03379453311949288</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.07794116237784454</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-0.06925704340063632</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-0.07989476773688065</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-0.04355676659122043</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.06122300321266128</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.04012323314519151</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.01433675039168847</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-0.0294508978788004</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>-0.0084534301090331</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.0397211438504792</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>-0.001282215844347512</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>-0.02053504113478866</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>-0.03751298064333231</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>-0.07838623657271349</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>-0.0697999305599728</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>-0.04794820066090733</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>-0.06147800981838802</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>-0.04176404365850139</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>-0.05586902355953871</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>-0.02371779787189787</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>-0.1329831381562228</v>
+      </c>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="n">
+        <v>-0.06373325308267841</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0.01043720874171328</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>-0.05937110471380613</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>-0.1021834435421214</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>-0.02445416233012043</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>-0.0329616219901876</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>-0.02005368959241327</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>-0.01160840814756803</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>-0.01342151019040649</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>-0.02608492581472976</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>-0.03040859748761626</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>-0.06487340880097037</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>-0.02287114959677083</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>-0.03125254350410422</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>-0.0007888698056834897</v>
+      </c>
+      <c r="BH19" t="inlineStr"/>
+      <c r="BI19" t="n">
+        <v>-0.04246720034477747</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>-0.02278002833181958</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>-0.08678411321078539</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>-0.1562426459835633</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>-0.1132778359331157</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>-0.06271795521414081</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>-0.07180143342967327</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>-0.01954605979712909</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>-0.0662768380826213</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>0.1542723461696314</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>-0.1636505626097335</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>-0.144813217252671</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>-0.1593155097802379</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>-0.09864017594399499</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>-0.09592601660963407</v>
+      </c>
+      <c r="BX19" t="inlineStr"/>
+      <c r="BY19" t="inlineStr"/>
+      <c r="BZ19" t="n">
+        <v>-0.1989079667865497</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>-0.1705186981725557</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>-0.1318834251773726</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>-0.04207484889672841</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>-0.09660870640585628</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>-0.1073291865276209</v>
+      </c>
+      <c r="CF19" t="n">
+        <v>-0.1330475704197411</v>
+      </c>
+      <c r="CG19" t="n">
+        <v>-0.0195491889635635</v>
+      </c>
+      <c r="CH19" t="n">
+        <v>-0.1678704093707344</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>-0.04261279284321606</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>-0.1804832041178805</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>-0.1032619301581077</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>-0.08267129755604241</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>-0.1488880925632268</v>
+      </c>
+      <c r="CN19" t="n">
+        <v>-0.08437813944998229</v>
+      </c>
+      <c r="CO19" t="n">
+        <v>-0.08267089120539861</v>
+      </c>
+      <c r="CP19" t="n">
+        <v>-0.1223343689327354</v>
+      </c>
+      <c r="CQ19" t="n">
+        <v>-0.2226579965583726</v>
+      </c>
+      <c r="CR19" t="inlineStr"/>
+      <c r="CS19" t="inlineStr"/>
+      <c r="CT19" t="inlineStr"/>
+      <c r="CU19" t="inlineStr"/>
+      <c r="CV19" t="inlineStr"/>
+      <c r="CW19" t="inlineStr"/>
+      <c r="CX19" t="inlineStr"/>
+      <c r="CY19" t="inlineStr"/>
+      <c r="CZ19" t="inlineStr"/>
+      <c r="DA19" t="inlineStr"/>
+      <c r="DB19" t="inlineStr"/>
+      <c r="DC19" t="inlineStr"/>
+      <c r="DD19" t="inlineStr"/>
+      <c r="DE19" t="inlineStr"/>
+      <c r="DF19" t="inlineStr"/>
+      <c r="DG19" t="inlineStr"/>
+      <c r="DH19" t="inlineStr"/>
+      <c r="DI19" t="inlineStr"/>
+      <c r="DJ19" t="inlineStr"/>
+      <c r="DK19" t="inlineStr"/>
+      <c r="DL19" t="inlineStr"/>
+      <c r="DM19" t="inlineStr"/>
+      <c r="DN19" t="inlineStr"/>
+      <c r="DO19" t="inlineStr"/>
+      <c r="DP19" t="inlineStr"/>
+      <c r="DQ19" t="inlineStr"/>
+      <c r="DR19" t="inlineStr"/>
+      <c r="DS19" t="inlineStr"/>
+      <c r="DT19" t="inlineStr"/>
+      <c r="DU19" t="inlineStr"/>
+      <c r="DV19" t="inlineStr"/>
+      <c r="DW19" t="inlineStr"/>
+      <c r="DX19" t="inlineStr"/>
+      <c r="DY19" t="inlineStr"/>
+      <c r="DZ19" t="inlineStr"/>
+      <c r="EA19" t="inlineStr"/>
+      <c r="EB19" t="inlineStr"/>
+      <c r="EC19" t="inlineStr"/>
+      <c r="ED19" t="inlineStr"/>
+      <c r="EE19" t="inlineStr"/>
+      <c r="EF19" t="inlineStr"/>
+      <c r="EG19" t="inlineStr"/>
+      <c r="EH19" t="inlineStr"/>
+      <c r="EI19" t="inlineStr"/>
+      <c r="EJ19" t="inlineStr"/>
+      <c r="EK19" t="inlineStr"/>
+      <c r="EL19" t="inlineStr"/>
+      <c r="EM19" t="inlineStr"/>
+      <c r="EN19" t="inlineStr"/>
+      <c r="EO19" t="inlineStr"/>
+      <c r="EP19" t="inlineStr"/>
+      <c r="EQ19" t="inlineStr"/>
+      <c r="ER19" t="inlineStr"/>
+      <c r="ES19" t="inlineStr"/>
+      <c r="ET19" t="inlineStr"/>
+      <c r="EU19" t="inlineStr"/>
+      <c r="EV19" t="inlineStr"/>
+      <c r="EW19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>2023 Q2→2023 Q3</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.04022467716414724</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.02805847290413066</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.05016528394086084</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-0.03854243239045019</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-0.04075116605634932</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-0.03495240120901233</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.003116604071953688</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-0.02229159792152835</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.06154924905194115</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.02155109496931473</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-0.005034219602331191</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.007027977626227866</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.002007606957262098</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-0.05682666569157568</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.02378432058700053</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.04905939771211809</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.03000792441508082</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.03453819720533247</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.01723905421415228</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-0.3986698476207451</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.02137032632375035</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-0.04241930835465624</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.07488369736148748</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.1466570129684399</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.02420091337456576</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.002643548372846638</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-0.009141921453425184</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>-0.005115173957209507</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.009946577403080248</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>-0.04085312759527504</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>-0.05390150481075739</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>-0.01490828594020055</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>-0.02030457437559008</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0.01978722280307377</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0.06517174705521711</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0.02188672648330492</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0.02641130180566176</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>-0.06550657542420613</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>-0.02633057127963934</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0.03036777960026793</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0.07535665466569785</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0.03173257747274949</v>
+      </c>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="n">
+        <v>-0.08674703152633523</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0.07732788676172841</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0.07737260700614712</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0.05845673969639442</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>-0.001312697357732873</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>-0.03794703347307671</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>-0.05023396848892858</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>-0.04649682229911001</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>-0.06760881507591421</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>-0.09054710040384784</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>-0.06557077648965759</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>-0.1058220163926293</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>-0.07260192834680268</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>-0.1151588542067019</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>-0.04452513953359905</v>
+      </c>
+      <c r="BH20" t="inlineStr"/>
+      <c r="BI20" t="n">
+        <v>0.01191961201515124</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>-0.02331107886844741</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>-0.03648464481451175</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>-0.04088118187785295</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>-0.07539856493870811</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>0.02737827514375102</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>0.0236823368483563</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>-0.03332018435118034</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>-0.04632425627146475</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>-0.4409045199678721</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>-0.07214386886162583</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>-0.02336167677410916</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>-0.01434798427060269</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>-0.1987078419638895</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>-0.1444634841302799</v>
+      </c>
+      <c r="BX20" t="inlineStr"/>
+      <c r="BY20" t="n">
+        <v>0.2673533899777221</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>-0.1394706216497905</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>-0.08790844839988043</v>
+      </c>
+      <c r="CB20" t="n">
+        <v>-0.09207379463680088</v>
+      </c>
+      <c r="CC20" t="n">
+        <v>-0.0547468304091705</v>
+      </c>
+      <c r="CD20" t="n">
+        <v>-0.01988947504044702</v>
+      </c>
+      <c r="CE20" t="n">
+        <v>-0.004406925114582627</v>
+      </c>
+      <c r="CF20" t="n">
+        <v>-0.1378682169248595</v>
+      </c>
+      <c r="CG20" t="n">
+        <v>-0.06888139890469169</v>
+      </c>
+      <c r="CH20" t="n">
+        <v>-0.08614763299363304</v>
+      </c>
+      <c r="CI20" t="n">
+        <v>-0.01110600128953632</v>
+      </c>
+      <c r="CJ20" t="n">
+        <v>-0.07377762264888243</v>
+      </c>
+      <c r="CK20" t="n">
+        <v>-0.05410165737899852</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>-0.06963483348052879</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>-0.01517276346904861</v>
+      </c>
+      <c r="CN20" t="n">
+        <v>0.004086029527279322</v>
+      </c>
+      <c r="CO20" t="n">
+        <v>-0.002791762959751587</v>
+      </c>
+      <c r="CP20" t="n">
+        <v>0.08342270454799117</v>
+      </c>
+      <c r="CQ20" t="n">
+        <v>-0.05368684209024543</v>
+      </c>
+      <c r="CR20" t="n">
+        <v>-0.1230721261981591</v>
+      </c>
+      <c r="CS20" t="n">
+        <v>-0.4127527360277448</v>
+      </c>
+      <c r="CT20" t="n">
+        <v>-0.1513700666950211</v>
+      </c>
+      <c r="CU20" t="inlineStr"/>
+      <c r="CV20" t="n">
+        <v>-0.06167249854608681</v>
+      </c>
+      <c r="CW20" t="n">
+        <v>-0.08016496111905269</v>
+      </c>
+      <c r="CX20" t="n">
+        <v>-0.1832496566910358</v>
+      </c>
+      <c r="CY20" t="n">
+        <v>-0.03305892421817536</v>
+      </c>
+      <c r="CZ20" t="n">
+        <v>0.02038900021098389</v>
+      </c>
+      <c r="DA20" t="inlineStr"/>
+      <c r="DB20" t="inlineStr"/>
+      <c r="DC20" t="inlineStr"/>
+      <c r="DD20" t="inlineStr"/>
+      <c r="DE20" t="inlineStr"/>
+      <c r="DF20" t="inlineStr"/>
+      <c r="DG20" t="inlineStr"/>
+      <c r="DH20" t="inlineStr"/>
+      <c r="DI20" t="inlineStr"/>
+      <c r="DJ20" t="inlineStr"/>
+      <c r="DK20" t="inlineStr"/>
+      <c r="DL20" t="inlineStr"/>
+      <c r="DM20" t="inlineStr"/>
+      <c r="DN20" t="inlineStr"/>
+      <c r="DO20" t="inlineStr"/>
+      <c r="DP20" t="inlineStr"/>
+      <c r="DQ20" t="inlineStr"/>
+      <c r="DR20" t="inlineStr"/>
+      <c r="DS20" t="inlineStr"/>
+      <c r="DT20" t="inlineStr"/>
+      <c r="DU20" t="inlineStr"/>
+      <c r="DV20" t="inlineStr"/>
+      <c r="DW20" t="inlineStr"/>
+      <c r="DX20" t="inlineStr"/>
+      <c r="DY20" t="inlineStr"/>
+      <c r="DZ20" t="inlineStr"/>
+      <c r="EA20" t="inlineStr"/>
+      <c r="EB20" t="inlineStr"/>
+      <c r="EC20" t="inlineStr"/>
+      <c r="ED20" t="inlineStr"/>
+      <c r="EE20" t="inlineStr"/>
+      <c r="EF20" t="inlineStr"/>
+      <c r="EG20" t="inlineStr"/>
+      <c r="EH20" t="inlineStr"/>
+      <c r="EI20" t="inlineStr"/>
+      <c r="EJ20" t="inlineStr"/>
+      <c r="EK20" t="inlineStr"/>
+      <c r="EL20" t="inlineStr"/>
+      <c r="EM20" t="inlineStr"/>
+      <c r="EN20" t="inlineStr"/>
+      <c r="EO20" t="inlineStr"/>
+      <c r="EP20" t="inlineStr"/>
+      <c r="EQ20" t="inlineStr"/>
+      <c r="ER20" t="inlineStr"/>
+      <c r="ES20" t="inlineStr"/>
+      <c r="ET20" t="inlineStr"/>
+      <c r="EU20" t="inlineStr"/>
+      <c r="EV20" t="inlineStr"/>
+      <c r="EW20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>2023 Q3→2023 Q4</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>-0.1407056267919318</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.1111598434723176</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.1469644908618344</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.0826557219640689</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0.09961760684833543</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-0.08764146441678644</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.07479508329495133</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-0.1231639344270938</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.02653815889762345</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-0.1008759434839375</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-0.174809955485097</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-0.1359955151247103</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-0.08065021964819774</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-0.09040071617130785</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-0.0879631911949339</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-0.08616138138610463</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-0.09498440701250832</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-0.1202947281732634</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-0.1618489064871973</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.07177797460679081</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-0.02126564533895525</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-0.0592782914437775</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-0.2253570561788871</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-0.2904052554756555</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.004484369902613139</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-0.2232032154053947</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-0.2250820205310173</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>-0.2027253933089286</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>-0.2094341239562256</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>-0.147191977470694</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>-0.1374025158210674</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>-0.09651192030064237</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>-0.1575752226424223</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>-0.161644307489575</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>-0.1668299487650939</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>-0.08528284136330466</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>-0.08270471762550979</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0.08593331424856654</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>-0.01149105887712931</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>-0.09284450624687768</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>-0.074502735736103</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0.007291124718856956</v>
+      </c>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="n">
+        <v>-0.04040673563812902</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>-0.2387603648721344</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>-0.02342156976168042</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>-0.08524597639028464</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>-0.05473363913421458</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>-0.1611784175312634</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>-0.1292870803591351</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>-0.1243045950372261</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>-0.2116071050494543</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>-0.2272407182982796</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>-0.2331956441722296</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>-0.1875031710086894</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>-0.212633492387547</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>-0.2089773724171815</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>-0.04663968210493685</v>
+      </c>
+      <c r="BH21" t="inlineStr"/>
+      <c r="BI21" t="n">
+        <v>-0.1011335231411259</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>0.0915617395011834</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>0.04768014398970966</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>0.008936961028677359</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>-0.06994059946193865</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>-0.04356841424384772</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>-0.005214485380381717</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>-0.0145175484006792</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>-0.02723700322541589</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>0.2165649546154196</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>-0.03910812823659082</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>-0.01300670720562103</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>0.02423375666307948</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>-0.09143464682493629</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>-0.1800690428159211</v>
+      </c>
+      <c r="BX21" t="inlineStr"/>
+      <c r="BY21" t="n">
+        <v>0.2684113243852471</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>-0.2243197587537482</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>-0.3871281853394644</v>
+      </c>
+      <c r="CB21" t="n">
+        <v>-0.4053034966951081</v>
+      </c>
+      <c r="CC21" t="n">
+        <v>-0.09501371716906082</v>
+      </c>
+      <c r="CD21" t="n">
+        <v>-0.07282016164619254</v>
+      </c>
+      <c r="CE21" t="n">
+        <v>-0.1067008090161163</v>
+      </c>
+      <c r="CF21" t="n">
+        <v>-0.1080708269176895</v>
+      </c>
+      <c r="CG21" t="n">
+        <v>-0.11020897832279</v>
+      </c>
+      <c r="CH21" t="n">
+        <v>-0.08517751526469652</v>
+      </c>
+      <c r="CI21" t="n">
+        <v>-0.1003471219733276</v>
+      </c>
+      <c r="CJ21" t="n">
+        <v>-0.1951510573285287</v>
+      </c>
+      <c r="CK21" t="n">
+        <v>-0.139336739521295</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>-0.1663252567904516</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>-0.1055592652276802</v>
+      </c>
+      <c r="CN21" t="n">
+        <v>-0.1193893745267793</v>
+      </c>
+      <c r="CO21" t="n">
+        <v>-0.08015445612577921</v>
+      </c>
+      <c r="CP21" t="n">
+        <v>-0.242468976799306</v>
+      </c>
+      <c r="CQ21" t="n">
+        <v>-0.01883538279773855</v>
+      </c>
+      <c r="CR21" t="n">
+        <v>0.0008213259518603522</v>
+      </c>
+      <c r="CS21" t="n">
+        <v>-0.226605452303529</v>
+      </c>
+      <c r="CT21" t="n">
+        <v>-0.04637581328991303</v>
+      </c>
+      <c r="CU21" t="n">
+        <v>-0.05195160640303964</v>
+      </c>
+      <c r="CV21" t="n">
+        <v>-0.07671171686028533</v>
+      </c>
+      <c r="CW21" t="n">
+        <v>-0.0622735556028271</v>
+      </c>
+      <c r="CX21" t="n">
+        <v>-0.1384316271662511</v>
+      </c>
+      <c r="CY21" t="n">
+        <v>-0.046988054340523</v>
+      </c>
+      <c r="CZ21" t="n">
+        <v>-0.1519798231856173</v>
+      </c>
+      <c r="DA21" t="inlineStr"/>
+      <c r="DB21" t="n">
+        <v>-0.08292264680133066</v>
+      </c>
+      <c r="DC21" t="inlineStr"/>
+      <c r="DD21" t="inlineStr"/>
+      <c r="DE21" t="n">
+        <v>-0.1617473729713366</v>
+      </c>
+      <c r="DF21" t="inlineStr"/>
+      <c r="DG21" t="inlineStr"/>
+      <c r="DH21" t="inlineStr"/>
+      <c r="DI21" t="inlineStr"/>
+      <c r="DJ21" t="inlineStr"/>
+      <c r="DK21" t="inlineStr"/>
+      <c r="DL21" t="inlineStr"/>
+      <c r="DM21" t="inlineStr"/>
+      <c r="DN21" t="inlineStr"/>
+      <c r="DO21" t="inlineStr"/>
+      <c r="DP21" t="inlineStr"/>
+      <c r="DQ21" t="inlineStr"/>
+      <c r="DR21" t="inlineStr"/>
+      <c r="DS21" t="inlineStr"/>
+      <c r="DT21" t="inlineStr"/>
+      <c r="DU21" t="inlineStr"/>
+      <c r="DV21" t="inlineStr"/>
+      <c r="DW21" t="inlineStr"/>
+      <c r="DX21" t="inlineStr"/>
+      <c r="DY21" t="inlineStr"/>
+      <c r="DZ21" t="inlineStr"/>
+      <c r="EA21" t="inlineStr"/>
+      <c r="EB21" t="inlineStr"/>
+      <c r="EC21" t="inlineStr"/>
+      <c r="ED21" t="inlineStr"/>
+      <c r="EE21" t="inlineStr"/>
+      <c r="EF21" t="inlineStr"/>
+      <c r="EG21" t="inlineStr"/>
+      <c r="EH21" t="inlineStr"/>
+      <c r="EI21" t="inlineStr"/>
+      <c r="EJ21" t="inlineStr"/>
+      <c r="EK21" t="inlineStr"/>
+      <c r="EL21" t="inlineStr"/>
+      <c r="EM21" t="inlineStr"/>
+      <c r="EN21" t="inlineStr"/>
+      <c r="EO21" t="inlineStr"/>
+      <c r="EP21" t="inlineStr"/>
+      <c r="EQ21" t="inlineStr"/>
+      <c r="ER21" t="inlineStr"/>
+      <c r="ES21" t="inlineStr"/>
+      <c r="ET21" t="inlineStr"/>
+      <c r="EU21" t="inlineStr"/>
+      <c r="EV21" t="inlineStr"/>
+      <c r="EW21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>2023 Q4→2024 Q1</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>-0.1179027241791148</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.06089809670728474</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.01652732588336825</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-0.08356785214034357</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.08051906638384398</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.09926681187552155</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.1522004702292898</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-0.1779493224218784</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-0.006507215660467303</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.3740172942096427</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-0.1032201939717394</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-0.1167552276517814</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-0.1636471157068682</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-0.1383180112771871</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-0.1809173412678673</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-0.1856465806387266</v>
+      </c>
+      <c r="R22" t="n">
+        <v>-0.1219532640845697</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-0.1139977405581059</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-0.1361995246862744</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.109745300692258</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.035173131802547</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-0.09268249558839337</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.0009526456481987466</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-0.2166768563486832</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-0.02252108680745035</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-0.1095500338881648</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>-0.08391924148973118</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>-0.119336845994817</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>-0.09009181334753613</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>-0.1345625127974923</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>-0.1512029936527872</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>-0.1615725763999887</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>-0.1068120117597742</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>-0.1081464931415494</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>-0.09249781273108049</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>-0.1535720291961198</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>-0.1542634632327839</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>-0.2260585187213211</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>-0.06398770867528292</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>-0.1782027112704787</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>-0.1120986978336411</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>-0.02631872580305128</v>
+      </c>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="n">
+        <v>-0.08155356726216745</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>-0.06330788944452959</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>-0.1841967674200564</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>-0.1480585816766631</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>-0.1374071554110685</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>-0.1512467613627244</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>-0.1944723053763715</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>-0.1546751029738287</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>-0.09788154018058304</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>-0.1190591581747729</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>-0.08138087946198702</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>-0.08392631261818728</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>-0.09887542189044574</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>-0.1146425795296748</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>-0.2169442434480091</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>0.003776922968722118</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>0.04414934198724474</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>-0.06911508944322708</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>-0.1432199648548655</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>-0.07486937021357853</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>-0.115980555446269</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>-0.1377014207667067</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>-0.1651176358921047</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>-0.011115066436167</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>-0.02067882924759967</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>0.08217318713510746</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>-0.1162776031077204</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>-0.1262339732951947</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>-0.3517586793289436</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>-0.09413704202578987</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>-0.1257537791165939</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>0.05577836334387598</v>
+      </c>
+      <c r="BY22" t="inlineStr"/>
+      <c r="BZ22" t="n">
+        <v>-0.1695307208339933</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>-0.07557089581949761</v>
+      </c>
+      <c r="CB22" t="n">
+        <v>-0.1188937227566482</v>
+      </c>
+      <c r="CC22" t="n">
+        <v>-0.09669168795036409</v>
+      </c>
+      <c r="CD22" t="n">
+        <v>-0.102123584407277</v>
+      </c>
+      <c r="CE22" t="n">
+        <v>-0.04719824151009888</v>
+      </c>
+      <c r="CF22" t="n">
+        <v>-0.07489934445236823</v>
+      </c>
+      <c r="CG22" t="n">
+        <v>-0.06353139204118019</v>
+      </c>
+      <c r="CH22" t="n">
+        <v>-0.04051929373521457</v>
+      </c>
+      <c r="CI22" t="n">
+        <v>-0.1408311977827621</v>
+      </c>
+      <c r="CJ22" t="n">
+        <v>-0.06383160695458301</v>
+      </c>
+      <c r="CK22" t="n">
+        <v>-0.08887877290681967</v>
+      </c>
+      <c r="CL22" t="n">
+        <v>-0.09175599226830844</v>
+      </c>
+      <c r="CM22" t="n">
+        <v>-0.1477114532569637</v>
+      </c>
+      <c r="CN22" t="n">
+        <v>-0.1984098083049375</v>
+      </c>
+      <c r="CO22" t="n">
+        <v>0.1968644722122725</v>
+      </c>
+      <c r="CP22" t="n">
+        <v>-0.09449865661271595</v>
+      </c>
+      <c r="CQ22" t="n">
+        <v>0.04135498694984374</v>
+      </c>
+      <c r="CR22" t="n">
+        <v>0.1880756880494339</v>
+      </c>
+      <c r="CS22" t="n">
+        <v>-0.09463147384425241</v>
+      </c>
+      <c r="CT22" t="n">
+        <v>0.04218224095761247</v>
+      </c>
+      <c r="CU22" t="n">
+        <v>-0.1193502766289889</v>
+      </c>
+      <c r="CV22" t="n">
+        <v>-0.07383971287246016</v>
+      </c>
+      <c r="CW22" t="n">
+        <v>-0.09601240538053446</v>
+      </c>
+      <c r="CX22" t="n">
+        <v>-0.07164199168319385</v>
+      </c>
+      <c r="CY22" t="n">
+        <v>0.001248456930874831</v>
+      </c>
+      <c r="CZ22" t="n">
+        <v>-0.1426047133829833</v>
+      </c>
+      <c r="DA22" t="inlineStr"/>
+      <c r="DB22" t="n">
+        <v>-0.1129652414039448</v>
+      </c>
+      <c r="DC22" t="inlineStr"/>
+      <c r="DD22" t="n">
+        <v>-0.1435804747159537</v>
+      </c>
+      <c r="DE22" t="n">
+        <v>-0.08602941727178504</v>
+      </c>
+      <c r="DF22" t="n">
+        <v>-0.04942064068976393</v>
+      </c>
+      <c r="DG22" t="inlineStr"/>
+      <c r="DH22" t="inlineStr"/>
+      <c r="DI22" t="n">
+        <v>-0.0833968880636311</v>
+      </c>
+      <c r="DJ22" t="n">
+        <v>-0.03383223457401652</v>
+      </c>
+      <c r="DK22" t="n">
+        <v>-0.09942841667638547</v>
+      </c>
+      <c r="DL22" t="inlineStr"/>
+      <c r="DM22" t="n">
+        <v>-0.1116820479981682</v>
+      </c>
+      <c r="DN22" t="n">
+        <v>-0.09964229531943225</v>
+      </c>
+      <c r="DO22" t="n">
+        <v>-0.1050394239073489</v>
+      </c>
+      <c r="DP22" t="n">
+        <v>-0.1483063905798181</v>
+      </c>
+      <c r="DQ22" t="n">
+        <v>-0.163098405326159</v>
+      </c>
+      <c r="DR22" t="n">
+        <v>-0.06995536605642272</v>
+      </c>
+      <c r="DS22" t="n">
+        <v>-0.095497011371517</v>
+      </c>
+      <c r="DT22" t="n">
+        <v>-0.03686280500604866</v>
+      </c>
+      <c r="DU22" t="inlineStr"/>
+      <c r="DV22" t="inlineStr"/>
+      <c r="DW22" t="inlineStr"/>
+      <c r="DX22" t="inlineStr"/>
+      <c r="DY22" t="inlineStr"/>
+      <c r="DZ22" t="inlineStr"/>
+      <c r="EA22" t="inlineStr"/>
+      <c r="EB22" t="inlineStr"/>
+      <c r="EC22" t="inlineStr"/>
+      <c r="ED22" t="inlineStr"/>
+      <c r="EE22" t="inlineStr"/>
+      <c r="EF22" t="inlineStr"/>
+      <c r="EG22" t="inlineStr"/>
+      <c r="EH22" t="inlineStr"/>
+      <c r="EI22" t="inlineStr"/>
+      <c r="EJ22" t="inlineStr"/>
+      <c r="EK22" t="inlineStr"/>
+      <c r="EL22" t="inlineStr"/>
+      <c r="EM22" t="inlineStr"/>
+      <c r="EN22" t="inlineStr"/>
+      <c r="EO22" t="inlineStr"/>
+      <c r="EP22" t="inlineStr"/>
+      <c r="EQ22" t="inlineStr"/>
+      <c r="ER22" t="inlineStr"/>
+      <c r="ES22" t="inlineStr"/>
+      <c r="ET22" t="inlineStr"/>
+      <c r="EU22" t="inlineStr"/>
+      <c r="EV22" t="inlineStr"/>
+      <c r="EW22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>2024 Q1→2024 Q2</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>-0.06346183979580733</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.0877469337272867</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.05819417610452504</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-0.09149365258153708</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.07836048175476673</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.09643260435894785</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.05227367347642797</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.009547096687404277</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-0.1133993098497186</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-0.3725598686447142</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-0.05540500745884547</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-0.08203266334199188</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-0.09953504699167848</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.07864656990284136</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-0.08303632891352297</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-0.05516346973783737</v>
+      </c>
+      <c r="R23" t="n">
+        <v>-0.1128171017083455</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-0.1248318561733921</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.05075622426736093</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.06389765296354533</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-0.08137418724495404</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-0.04879382744817651</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-0.1431618834539101</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.009161312337901073</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-0.1363408508557384</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-0.06842537252278191</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>-0.0593554947211663</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>-0.03641610200045786</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>-0.03587220232432919</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>-0.08010307211012169</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>-0.03303959246242716</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>-0.07909413046811054</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>-0.05818426928430931</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>-0.04668815704221174</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>-0.07136448620797076</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>-0.0601782194112026</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>-0.1110325492927551</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>-0.06157911619851308</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>-0.126320199751321</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0.1190001834353307</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>-0.1484909360688409</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>-0.07260903175796241</v>
+      </c>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="n">
+        <v>-0.03861483612777938</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>-0.04837879977526693</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>-0.07443492892477543</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>-0.04512679930028174</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>-0.1253600009301712</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>-0.0555209881204588</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>-0.03569575908067613</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>-0.03383824463197715</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0.0002311680602087307</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>-0.02351636862632844</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0.01697705305073516</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>-0.01079083529329417</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>-0.02107076383108542</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>-0.01607724715742798</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>-0.1446040099671864</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>-0.00242109109599653</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>0.3452440795516774</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>0.2249292146440212</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>-0.2250864073059793</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>0.1105943139026602</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>-0.2130403549381024</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>-0.2145658229136878</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>-0.2154514111455414</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>-0.01283673219645909</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>-0.007178646110808984</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>-0.1559474237132079</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>-0.190605590227265</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>-0.2037672723510715</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>0.1526862707623149</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>-0.1486155988706743</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>-0.07680138352411259</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>-0.133951035522303</v>
+      </c>
+      <c r="BY23" t="inlineStr"/>
+      <c r="BZ23" t="n">
+        <v>-0.0836545840373013</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>0.004603324395531239</v>
+      </c>
+      <c r="CB23" t="n">
+        <v>-0.005949212911815493</v>
+      </c>
+      <c r="CC23" t="n">
+        <v>-0.1027021743463399</v>
+      </c>
+      <c r="CD23" t="n">
+        <v>-0.09799756823013261</v>
+      </c>
+      <c r="CE23" t="n">
+        <v>-0.01684293963962435</v>
+      </c>
+      <c r="CF23" t="n">
+        <v>-0.04396539742112981</v>
+      </c>
+      <c r="CG23" t="n">
+        <v>-0.1186165999774733</v>
+      </c>
+      <c r="CH23" t="n">
+        <v>-0.05448357434369111</v>
+      </c>
+      <c r="CI23" t="n">
+        <v>-0.06216368225598146</v>
+      </c>
+      <c r="CJ23" t="n">
+        <v>-0.04873147329700878</v>
+      </c>
+      <c r="CK23" t="n">
+        <v>-0.03802830592233963</v>
+      </c>
+      <c r="CL23" t="n">
+        <v>-0.04347351599966043</v>
+      </c>
+      <c r="CM23" t="n">
+        <v>-0.06135870740331661</v>
+      </c>
+      <c r="CN23" t="n">
+        <v>-0.01936519969717843</v>
+      </c>
+      <c r="CO23" t="n">
+        <v>-0.05009903391876325</v>
+      </c>
+      <c r="CP23" t="n">
+        <v>-0.04700052021176848</v>
+      </c>
+      <c r="CQ23" t="n">
+        <v>-0.03337128319943083</v>
+      </c>
+      <c r="CR23" t="n">
+        <v>0.2029480869007569</v>
+      </c>
+      <c r="CS23" t="n">
+        <v>0.08510106346524982</v>
+      </c>
+      <c r="CT23" t="n">
+        <v>0.05224666892176266</v>
+      </c>
+      <c r="CU23" t="n">
+        <v>-0.1165270381037438</v>
+      </c>
+      <c r="CV23" t="n">
+        <v>-0.116240177854821</v>
+      </c>
+      <c r="CW23" t="n">
+        <v>-0.06778806407477322</v>
+      </c>
+      <c r="CX23" t="n">
+        <v>-0.123824112749686</v>
+      </c>
+      <c r="CY23" t="n">
+        <v>0.0310379625344801</v>
+      </c>
+      <c r="CZ23" t="n">
+        <v>-0.05738790040115926</v>
+      </c>
+      <c r="DA23" t="inlineStr"/>
+      <c r="DB23" t="n">
+        <v>-0.07658304075362743</v>
+      </c>
+      <c r="DC23" t="n">
+        <v>0.05967033629626961</v>
+      </c>
+      <c r="DD23" t="n">
+        <v>-0.07719032662622727</v>
+      </c>
+      <c r="DE23" t="n">
+        <v>0.01079497498951199</v>
+      </c>
+      <c r="DF23" t="n">
+        <v>-0.01441917574173157</v>
+      </c>
+      <c r="DG23" t="n">
+        <v>-0.02161826131248823</v>
+      </c>
+      <c r="DH23" t="n">
+        <v>-0.01426272461464784</v>
+      </c>
+      <c r="DI23" t="n">
+        <v>-0.01379332213233653</v>
+      </c>
+      <c r="DJ23" t="n">
+        <v>-0.1002751432745468</v>
+      </c>
+      <c r="DK23" t="n">
+        <v>-0.03255776513848829</v>
+      </c>
+      <c r="DL23" t="n">
+        <v>-0.05201205863134639</v>
+      </c>
+      <c r="DM23" t="n">
+        <v>-0.0538812960692816</v>
+      </c>
+      <c r="DN23" t="n">
+        <v>-0.026182657251546</v>
+      </c>
+      <c r="DO23" t="n">
+        <v>-0.05618887229822622</v>
+      </c>
+      <c r="DP23" t="n">
+        <v>-0.0003844479100827414</v>
+      </c>
+      <c r="DQ23" t="n">
+        <v>-0.0585346281616399</v>
+      </c>
+      <c r="DR23" t="n">
+        <v>-0.03995319274748876</v>
+      </c>
+      <c r="DS23" t="n">
+        <v>-0.0372153095733001</v>
+      </c>
+      <c r="DT23" t="n">
+        <v>-0.009019268034549555</v>
+      </c>
+      <c r="DU23" t="n">
+        <v>-0.110623828005723</v>
+      </c>
+      <c r="DV23" t="inlineStr"/>
+      <c r="DW23" t="inlineStr"/>
+      <c r="DX23" t="inlineStr"/>
+      <c r="DY23" t="inlineStr"/>
+      <c r="DZ23" t="inlineStr"/>
+      <c r="EA23" t="inlineStr"/>
+      <c r="EB23" t="inlineStr"/>
+      <c r="EC23" t="inlineStr"/>
+      <c r="ED23" t="inlineStr"/>
+      <c r="EE23" t="inlineStr"/>
+      <c r="EF23" t="inlineStr"/>
+      <c r="EG23" t="inlineStr"/>
+      <c r="EH23" t="inlineStr"/>
+      <c r="EI23" t="inlineStr"/>
+      <c r="EJ23" t="inlineStr"/>
+      <c r="EK23" t="inlineStr"/>
+      <c r="EL23" t="inlineStr"/>
+      <c r="EM23" t="inlineStr"/>
+      <c r="EN23" t="inlineStr"/>
+      <c r="EO23" t="inlineStr"/>
+      <c r="EP23" t="inlineStr"/>
+      <c r="EQ23" t="inlineStr"/>
+      <c r="ER23" t="inlineStr"/>
+      <c r="ES23" t="inlineStr"/>
+      <c r="ET23" t="inlineStr"/>
+      <c r="EU23" t="inlineStr"/>
+      <c r="EV23" t="inlineStr"/>
+      <c r="EW23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>2024 Q2→2024 Q3</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.05197717435426163</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.04226275112393996</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.02036112073086738</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.01294265524544524</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.01736965734878471</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.0359263467493145</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.05492986764035024</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.04848687346296732</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-0.004748193777301957</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.1324522768447896</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.0026911562239329</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.0424511957056195</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.02715668034264596</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.04118690502814193</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.06527831370587744</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.001105499974401347</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.007774961746372711</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.04917252041144149</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.01866617164992768</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.2035567873812676</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-0.04026488889780211</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.0112831320752953</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-0.1349778178834908</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0.02432766702403466</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-0.05409386138562944</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.06241571397086787</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.06079027757599942</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0.0832541389508652</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.02126634744136702</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0.0345671882151759</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0.04143294221954008</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0.006184211621298452</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0.02570642705650439</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0.01690015004714951</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0.04319040544285091</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>-0.01245442498638027</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0.01516123140256642</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>-0.03429389606099331</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0.1008046991219658</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>-0.1688455817111834</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0.1118639282805116</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>-0.04100784176413796</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>-0.1096915515383401</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>-0.1836844770611492</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>-0.02689493578709889</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>-0.04870337397132918</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>-0.02793872757133631</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0.0131552312784553</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0.06706577358484722</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0.03343403773402009</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0.01125382825672805</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>-0.02531399796941169</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0.02306131505075726</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>-0.014169688620985</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0.004185684582930449</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0.02410788175418332</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>0.02320375854938828</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0.06274939410344071</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>0.02021329252046389</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>0.05364719015138864</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>-0.005540180375614767</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>-0.0604003646672977</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>0.004236297227421026</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>-0.04418959109259291</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>-0.04845642805768069</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>-0.07576712861790469</v>
+      </c>
+      <c r="BP24" t="inlineStr"/>
+      <c r="BQ24" t="n">
+        <v>0.01395563038983205</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>-0.08944621061876035</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>-0.06091985303648784</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>-0.051284195441057</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>0.08180174831672904</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>0.1282280723381506</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>0.03883321207864388</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>0.04650877904856721</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>0.03437221429036352</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>0.03895881196852002</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>0.001373755250546616</v>
+      </c>
+      <c r="CB24" t="n">
+        <v>-0.001924254945192772</v>
+      </c>
+      <c r="CC24" t="n">
+        <v>-0.0220904121766603</v>
+      </c>
+      <c r="CD24" t="n">
+        <v>0.01818736020361023</v>
+      </c>
+      <c r="CE24" t="n">
+        <v>-0.09377251071759218</v>
+      </c>
+      <c r="CF24" t="n">
+        <v>-0.05168294284117181</v>
+      </c>
+      <c r="CG24" t="n">
+        <v>0.0006481454429536626</v>
+      </c>
+      <c r="CH24" t="n">
+        <v>-0.06034381147850354</v>
+      </c>
+      <c r="CI24" t="n">
+        <v>0.01048427937913576</v>
+      </c>
+      <c r="CJ24" t="n">
+        <v>-0.04606500142030256</v>
+      </c>
+      <c r="CK24" t="n">
+        <v>-0.05268906666160778</v>
+      </c>
+      <c r="CL24" t="n">
+        <v>-0.01610629464981983</v>
+      </c>
+      <c r="CM24" t="n">
+        <v>0.01360301056172819</v>
+      </c>
+      <c r="CN24" t="n">
+        <v>0.01647002097956385</v>
+      </c>
+      <c r="CO24" t="n">
+        <v>-0.02634523902365959</v>
+      </c>
+      <c r="CP24" t="n">
+        <v>-0.005817125384064425</v>
+      </c>
+      <c r="CQ24" t="n">
+        <v>-0.1270141383922576</v>
+      </c>
+      <c r="CR24" t="n">
+        <v>-0.259216158804521</v>
+      </c>
+      <c r="CS24" t="n">
+        <v>-0.1334449966332425</v>
+      </c>
+      <c r="CT24" t="inlineStr"/>
+      <c r="CU24" t="n">
+        <v>-0.03382364517901948</v>
+      </c>
+      <c r="CV24" t="n">
+        <v>-0.07181943671244806</v>
+      </c>
+      <c r="CW24" t="n">
+        <v>-0.02166741841090314</v>
+      </c>
+      <c r="CX24" t="n">
+        <v>-0.01573368549901133</v>
+      </c>
+      <c r="CY24" t="n">
+        <v>0.009736341825410832</v>
+      </c>
+      <c r="CZ24" t="n">
+        <v>-0.02421159090112202</v>
+      </c>
+      <c r="DA24" t="n">
+        <v>-0.006233595935364988</v>
+      </c>
+      <c r="DB24" t="n">
+        <v>-0.1104644438268165</v>
+      </c>
+      <c r="DC24" t="n">
+        <v>-0.3708609769234226</v>
+      </c>
+      <c r="DD24" t="n">
+        <v>0.001752698228599137</v>
+      </c>
+      <c r="DE24" t="n">
+        <v>-0.06217785987629032</v>
+      </c>
+      <c r="DF24" t="n">
+        <v>0.06326852775195668</v>
+      </c>
+      <c r="DG24" t="n">
+        <v>-0.004186447846193708</v>
+      </c>
+      <c r="DH24" t="n">
+        <v>-0.03513957429632963</v>
+      </c>
+      <c r="DI24" t="n">
+        <v>-0.02559178809504736</v>
+      </c>
+      <c r="DJ24" t="n">
+        <v>-0.0609835043825333</v>
+      </c>
+      <c r="DK24" t="n">
+        <v>-0.03241703512425609</v>
+      </c>
+      <c r="DL24" t="n">
+        <v>-0.1436056305313089</v>
+      </c>
+      <c r="DM24" t="n">
+        <v>-0.0107161522402146</v>
+      </c>
+      <c r="DN24" t="n">
+        <v>-0.0489405587128191</v>
+      </c>
+      <c r="DO24" t="n">
+        <v>-0.07270313439519072</v>
+      </c>
+      <c r="DP24" t="n">
+        <v>-0.08862853160036988</v>
+      </c>
+      <c r="DQ24" t="n">
+        <v>-0.06517136474417473</v>
+      </c>
+      <c r="DR24" t="n">
+        <v>-0.04205976479993279</v>
+      </c>
+      <c r="DS24" t="n">
+        <v>-0.0522393543669617</v>
+      </c>
+      <c r="DT24" t="n">
+        <v>0.04363728508966602</v>
+      </c>
+      <c r="DU24" t="n">
+        <v>-0.07202137957186405</v>
+      </c>
+      <c r="DV24" t="n">
+        <v>-0.02595826167122439</v>
+      </c>
+      <c r="DW24" t="n">
+        <v>-0.1648454012803429</v>
+      </c>
+      <c r="DX24" t="inlineStr"/>
+      <c r="DY24" t="inlineStr"/>
+      <c r="DZ24" t="n">
+        <v>-0.0875284833632346</v>
+      </c>
+      <c r="EA24" t="n">
+        <v>0.2422945360185169</v>
+      </c>
+      <c r="EB24" t="n">
+        <v>0.05888827484055525</v>
+      </c>
+      <c r="EC24" t="inlineStr"/>
+      <c r="ED24" t="inlineStr"/>
+      <c r="EE24" t="inlineStr"/>
+      <c r="EF24" t="inlineStr"/>
+      <c r="EG24" t="inlineStr"/>
+      <c r="EH24" t="inlineStr"/>
+      <c r="EI24" t="inlineStr"/>
+      <c r="EJ24" t="inlineStr"/>
+      <c r="EK24" t="inlineStr"/>
+      <c r="EL24" t="inlineStr"/>
+      <c r="EM24" t="inlineStr"/>
+      <c r="EN24" t="inlineStr"/>
+      <c r="EO24" t="inlineStr"/>
+      <c r="EP24" t="inlineStr"/>
+      <c r="EQ24" t="inlineStr"/>
+      <c r="ER24" t="inlineStr"/>
+      <c r="ES24" t="inlineStr"/>
+      <c r="ET24" t="inlineStr"/>
+      <c r="EU24" t="inlineStr"/>
+      <c r="EV24" t="inlineStr"/>
+      <c r="EW24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>2024 Q3→2024 Q4</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>-0.0165692585801116</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.04168688312371494</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-0.04890440454539124</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.03933466677428044</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.002060770541314483</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.03811286458887686</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.08940250324956978</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.05475880262514377</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.03407524730560141</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.02320560916287562</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.009292351451875902</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.02476683455862361</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.04488321549522745</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.0338029639448445</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-0.01321719872630744</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-0.02083170795777534</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.01368902153071438</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.0032463287996638</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.01350300685922345</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.07333265368589448</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-0.0104400649966836</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.03196379897598334</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.04677958610675681</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0.0566656834553747</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0.01123059446806618</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-0.03395279466090617</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>-0.02125263858293014</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>-0.02466565750109595</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>-0.0221508140551343</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>-0.0264199248082404</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>-0.05134481629857568</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>-0.01432625301844137</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>-0.02350403391261846</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>-0.0267920185300019</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>-0.04786789416717774</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>-0.01915781098454694</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>-0.01006650499192929</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0.02966178373443196</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>-0.101273412512314</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0.02379528172155698</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>-0.1064983183534771</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>-0.03256159420213134</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>-0.1232233427916993</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0.008276611835960956</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0.1082366636049112</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>-0.1014937658463335</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>-0.0996684568240207</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>-0.08162853046562635</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>-0.09894493073869715</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>-0.07835207980215397</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>-0.1220076367624507</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>-0.09632330820419277</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>-0.09183723385423814</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>-0.1051898256032748</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>-0.118960798597004</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>-0.09904255023492148</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>-0.1261300065363491</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0.09113531219870463</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>-0.007287903157591202</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>-0.02200285951124403</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>-0.006502577487567329</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>0.00347797973290831</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>0.00421842669151129</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>-0.01274978868668342</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>0.02197584475691539</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>0.08635343894365732</v>
+      </c>
+      <c r="BP25" t="inlineStr"/>
+      <c r="BQ25" t="n">
+        <v>-0.03058763297274236</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>0.1112850688762625</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>-0.02277815275566653</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>-0.01509624073166371</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>-0.06178537057045652</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>-0.02016218070009845</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>-0.1956421616263233</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>0.2802014545163338</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>-0.0125370769621318</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>-0.1905553617210582</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>0.02923978156263285</v>
+      </c>
+      <c r="CB25" t="n">
+        <v>0.01846419821163714</v>
+      </c>
+      <c r="CC25" t="n">
+        <v>-0.07870530545871546</v>
+      </c>
+      <c r="CD25" t="n">
+        <v>-0.0940544892201034</v>
+      </c>
+      <c r="CE25" t="n">
+        <v>-0.04241066145451633</v>
+      </c>
+      <c r="CF25" t="n">
+        <v>-0.1376419944490239</v>
+      </c>
+      <c r="CG25" t="n">
+        <v>-0.0446695497115428</v>
+      </c>
+      <c r="CH25" t="n">
+        <v>-0.1533715137704768</v>
+      </c>
+      <c r="CI25" t="n">
+        <v>-0.07640016269952632</v>
+      </c>
+      <c r="CJ25" t="n">
+        <v>-0.1434914637058071</v>
+      </c>
+      <c r="CK25" t="n">
+        <v>-0.1558397743113868</v>
+      </c>
+      <c r="CL25" t="n">
+        <v>-0.1937375874082132</v>
+      </c>
+      <c r="CM25" t="n">
+        <v>-0.2036847990747708</v>
+      </c>
+      <c r="CN25" t="n">
+        <v>-0.08138743629773959</v>
+      </c>
+      <c r="CO25" t="n">
+        <v>0.06949740807513916</v>
+      </c>
+      <c r="CP25" t="n">
+        <v>-0.1737939294718949</v>
+      </c>
+      <c r="CQ25" t="n">
+        <v>0.06345525745391623</v>
+      </c>
+      <c r="CR25" t="n">
+        <v>0.8719976679068502</v>
+      </c>
+      <c r="CS25" t="n">
+        <v>-0.08921987080053384</v>
+      </c>
+      <c r="CT25" t="inlineStr"/>
+      <c r="CU25" t="n">
+        <v>0.01410958151631991</v>
+      </c>
+      <c r="CV25" t="n">
+        <v>-0.01611063579425398</v>
+      </c>
+      <c r="CW25" t="n">
+        <v>-0.05936732222821917</v>
+      </c>
+      <c r="CX25" t="n">
+        <v>0.0279824861856941</v>
+      </c>
+      <c r="CY25" t="n">
+        <v>-0.03972126430248668</v>
+      </c>
+      <c r="CZ25" t="n">
+        <v>-0.004573257564561395</v>
+      </c>
+      <c r="DA25" t="n">
+        <v>0.6076282912893038</v>
+      </c>
+      <c r="DB25" t="n">
+        <v>-0.07394813316108895</v>
+      </c>
+      <c r="DC25" t="n">
+        <v>-0.1035226322757739</v>
+      </c>
+      <c r="DD25" t="n">
+        <v>-0.06763014955805957</v>
+      </c>
+      <c r="DE25" t="n">
+        <v>-0.1718659120043542</v>
+      </c>
+      <c r="DF25" t="n">
+        <v>-0.2747720390749455</v>
+      </c>
+      <c r="DG25" t="n">
+        <v>-0.003189574192065336</v>
+      </c>
+      <c r="DH25" t="n">
+        <v>0.03626060780269125</v>
+      </c>
+      <c r="DI25" t="n">
+        <v>-0.1010343190563097</v>
+      </c>
+      <c r="DJ25" t="n">
+        <v>-0.0008685618403667661</v>
+      </c>
+      <c r="DK25" t="n">
+        <v>-0.1196422500266578</v>
+      </c>
+      <c r="DL25" t="n">
+        <v>-0.03107762903032363</v>
+      </c>
+      <c r="DM25" t="n">
+        <v>-0.106597477920479</v>
+      </c>
+      <c r="DN25" t="n">
+        <v>-0.1047574568542524</v>
+      </c>
+      <c r="DO25" t="n">
+        <v>-0.1716302935312415</v>
+      </c>
+      <c r="DP25" t="n">
+        <v>-0.2149817394949984</v>
+      </c>
+      <c r="DQ25" t="n">
+        <v>-0.1348353586468072</v>
+      </c>
+      <c r="DR25" t="n">
+        <v>-0.1437970421783215</v>
+      </c>
+      <c r="DS25" t="n">
+        <v>-0.1658011426255985</v>
+      </c>
+      <c r="DT25" t="n">
+        <v>-0.08752066268356362</v>
+      </c>
+      <c r="DU25" t="n">
+        <v>-0.1609635084000534</v>
+      </c>
+      <c r="DV25" t="n">
+        <v>-0.06317105905801945</v>
+      </c>
+      <c r="DW25" t="n">
+        <v>-0.09122844910929562</v>
+      </c>
+      <c r="DX25" t="inlineStr"/>
+      <c r="DY25" t="inlineStr"/>
+      <c r="DZ25" t="n">
+        <v>-0.07932199429421694</v>
+      </c>
+      <c r="EA25" t="n">
+        <v>0.2262658987067425</v>
+      </c>
+      <c r="EB25" t="n">
+        <v>-0.02225543900568194</v>
+      </c>
+      <c r="EC25" t="inlineStr"/>
+      <c r="ED25" t="inlineStr"/>
+      <c r="EE25" t="n">
+        <v>-0.2493925559534036</v>
+      </c>
+      <c r="EF25" t="inlineStr"/>
+      <c r="EG25" t="inlineStr"/>
+      <c r="EH25" t="inlineStr"/>
+      <c r="EI25" t="inlineStr"/>
+      <c r="EJ25" t="inlineStr"/>
+      <c r="EK25" t="inlineStr"/>
+      <c r="EL25" t="inlineStr"/>
+      <c r="EM25" t="inlineStr"/>
+      <c r="EN25" t="inlineStr"/>
+      <c r="EO25" t="inlineStr"/>
+      <c r="EP25" t="inlineStr"/>
+      <c r="EQ25" t="inlineStr"/>
+      <c r="ER25" t="inlineStr"/>
+      <c r="ES25" t="inlineStr"/>
+      <c r="ET25" t="inlineStr"/>
+      <c r="EU25" t="inlineStr"/>
+      <c r="EV25" t="inlineStr"/>
+      <c r="EW25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>2024 Q4→2025 Q1</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>-0.0390416908450284</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.05813713142880772</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-0.09465636919883114</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.08089767651925506</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.03807714796456985</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.1113600244714634</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.1470191802800764</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-0.1678583264599283</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-0.03004132445039431</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.04204214998292866</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-0.1040274691383596</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-0.1042115175252665</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.1065309644359527</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.07398285556764961</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-0.1118446158557758</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-0.09439013755587489</v>
+      </c>
+      <c r="R26" t="n">
+        <v>-0.1030899430156174</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.1143616877196116</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.1311450155293432</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.1918210801851679</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-0.03620676889513597</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-0.1303212519264552</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-0.004209055670342465</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0.05362615135354432</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-0.01757780714503721</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-0.09489237345473445</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>-0.1312231110786213</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>-0.1168068172741563</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>-0.1405876896922367</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>-0.1476108031848478</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>-0.1189066090018178</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>-0.1489253649689486</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>-0.1729437274045811</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>-0.1385717379162488</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>-0.1438340454960496</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>-0.1384564544530367</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>-0.1261800138528137</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0.05275056538552914</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0.02317063807859299</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0.02919962525791053</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>-0.06928895734651785</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>-0.02140826126588102</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>-0.3999330590012491</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0.07356436585624593</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>-0.08034085196796514</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>-0.06049162835508426</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>-0.1207407527469888</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>-0.133077359062753</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>-0.1978694892215547</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>-0.1855047700456494</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>-0.1691424179477066</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>-0.181836889061473</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>-0.1639056850572969</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>-0.1146647171958159</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>-0.1105755547559744</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>-0.1441560870959959</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>-0.1258058695806401</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>-0.04657989821898223</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>-0.01898791224469143</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>0.06472214455269576</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>-0.007173853328676927</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>-0.05236447186017035</v>
+      </c>
+      <c r="BL26" t="inlineStr"/>
+      <c r="BM26" t="n">
+        <v>-0.03095525749416961</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>-0.0700145043419127</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>-0.08919164523554279</v>
+      </c>
+      <c r="BP26" t="inlineStr"/>
+      <c r="BQ26" t="n">
+        <v>-0.04182651494626022</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>0.05640170604411043</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>0.02589363106295473</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>-0.01971456885241096</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>0.007528906871463903</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>-0.1851415525232891</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>-0.01693179500339603</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>-0.01741676844144902</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>-0.01268257299004194</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>0.1028164474130513</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>-0.01286956251671434</v>
+      </c>
+      <c r="CB26" t="n">
+        <v>-0.1251680543161973</v>
+      </c>
+      <c r="CC26" t="n">
+        <v>-0.1584802750450072</v>
+      </c>
+      <c r="CD26" t="n">
+        <v>-0.1684691373596579</v>
+      </c>
+      <c r="CE26" t="n">
+        <v>-0.1511705861696635</v>
+      </c>
+      <c r="CF26" t="n">
+        <v>-0.04471624295896781</v>
+      </c>
+      <c r="CG26" t="n">
+        <v>-0.1662238429218572</v>
+      </c>
+      <c r="CH26" t="n">
+        <v>-0.07439418343388127</v>
+      </c>
+      <c r="CI26" t="n">
+        <v>-0.1607035806690913</v>
+      </c>
+      <c r="CJ26" t="n">
+        <v>-0.06396622574447797</v>
+      </c>
+      <c r="CK26" t="n">
+        <v>-0.1093799195814222</v>
+      </c>
+      <c r="CL26" t="n">
+        <v>-0.1006814059945436</v>
+      </c>
+      <c r="CM26" t="n">
+        <v>-0.123803502025674</v>
+      </c>
+      <c r="CN26" t="n">
+        <v>-0.0714613658291654</v>
+      </c>
+      <c r="CO26" t="n">
+        <v>-0.002428645578921973</v>
+      </c>
+      <c r="CP26" t="n">
+        <v>-0.1042945885231097</v>
+      </c>
+      <c r="CQ26" t="inlineStr"/>
+      <c r="CR26" t="n">
+        <v>-0.6261735356177338</v>
+      </c>
+      <c r="CS26" t="n">
+        <v>0.1526682956183611</v>
+      </c>
+      <c r="CT26" t="inlineStr"/>
+      <c r="CU26" t="n">
+        <v>-0.1548114812651109</v>
+      </c>
+      <c r="CV26" t="n">
+        <v>-0.1060700253625182</v>
+      </c>
+      <c r="CW26" t="n">
+        <v>-0.05937428484828366</v>
+      </c>
+      <c r="CX26" t="n">
+        <v>-0.07156323824044808</v>
+      </c>
+      <c r="CY26" t="n">
+        <v>0.1999603930248153</v>
+      </c>
+      <c r="CZ26" t="n">
+        <v>-0.05506212520808429</v>
+      </c>
+      <c r="DA26" t="n">
+        <v>-0.6427207058254778</v>
+      </c>
+      <c r="DB26" t="n">
+        <v>0.1518761567629809</v>
+      </c>
+      <c r="DC26" t="n">
+        <v>0.2323480870432819</v>
+      </c>
+      <c r="DD26" t="n">
+        <v>-0.01008039552194528</v>
+      </c>
+      <c r="DE26" t="n">
+        <v>0.03734449867927569</v>
+      </c>
+      <c r="DF26" t="n">
+        <v>-0.2495736903667947</v>
+      </c>
+      <c r="DG26" t="n">
+        <v>0.001332537709496151</v>
+      </c>
+      <c r="DH26" t="n">
+        <v>-0.03902364308048334</v>
+      </c>
+      <c r="DI26" t="n">
+        <v>-0.1067694698268795</v>
+      </c>
+      <c r="DJ26" t="n">
+        <v>-0.1765980038646644</v>
+      </c>
+      <c r="DK26" t="n">
+        <v>-0.09702305650483201</v>
+      </c>
+      <c r="DL26" t="n">
+        <v>-0.08715101852892637</v>
+      </c>
+      <c r="DM26" t="n">
+        <v>-0.07698453725843013</v>
+      </c>
+      <c r="DN26" t="n">
+        <v>-0.08532304297386162</v>
+      </c>
+      <c r="DO26" t="n">
+        <v>-0.07591566874474331</v>
+      </c>
+      <c r="DP26" t="n">
+        <v>-0.1048609753308147</v>
+      </c>
+      <c r="DQ26" t="n">
+        <v>-0.08646807790671662</v>
+      </c>
+      <c r="DR26" t="n">
+        <v>-0.06583926331357226</v>
+      </c>
+      <c r="DS26" t="n">
+        <v>-0.06574710623980184</v>
+      </c>
+      <c r="DT26" t="n">
+        <v>-0.02743091296786471</v>
+      </c>
+      <c r="DU26" t="n">
+        <v>0.09113791072778987</v>
+      </c>
+      <c r="DV26" t="n">
+        <v>-0.06743234399580977</v>
+      </c>
+      <c r="DW26" t="n">
+        <v>0.06755183525165709</v>
+      </c>
+      <c r="DX26" t="inlineStr"/>
+      <c r="DY26" t="inlineStr"/>
+      <c r="DZ26" t="n">
+        <v>-0.0402823421399372</v>
+      </c>
+      <c r="EA26" t="n">
+        <v>-0.2436024851332625</v>
+      </c>
+      <c r="EB26" t="n">
+        <v>-0.03262442098833862</v>
+      </c>
+      <c r="EC26" t="inlineStr"/>
+      <c r="ED26" t="inlineStr"/>
+      <c r="EE26" t="n">
+        <v>-0.1163227950390953</v>
+      </c>
+      <c r="EF26" t="inlineStr"/>
+      <c r="EG26" t="n">
+        <v>-0.1673653192477857</v>
+      </c>
+      <c r="EH26" t="n">
+        <v>-0.09888526996768032</v>
+      </c>
+      <c r="EI26" t="n">
+        <v>-0.04798116462959801</v>
+      </c>
+      <c r="EJ26" t="n">
+        <v>-0.1412396195410208</v>
+      </c>
+      <c r="EK26" t="n">
+        <v>-0.118836695445462</v>
+      </c>
+      <c r="EL26" t="n">
+        <v>-0.1321439459850522</v>
+      </c>
+      <c r="EM26" t="n">
+        <v>-0.1291480318825382</v>
+      </c>
+      <c r="EN26" t="n">
+        <v>-0.1880595517773918</v>
+      </c>
+      <c r="EO26" t="n">
+        <v>-0.1644145855954058</v>
+      </c>
+      <c r="EP26" t="n">
+        <v>-0.09099257827077523</v>
+      </c>
+      <c r="EQ26" t="n">
+        <v>-0.1269857111347417</v>
+      </c>
+      <c r="ER26" t="inlineStr"/>
+      <c r="ES26" t="n">
+        <v>-0.0301181149733436</v>
+      </c>
+      <c r="ET26" t="inlineStr"/>
+      <c r="EU26" t="inlineStr"/>
+      <c r="EV26" t="inlineStr"/>
+      <c r="EW26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>2025 Q1→2025 Q2</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>-0.03981256606653449</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.0449337089631543</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.01359979336734352</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-0.03111919866631307</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.03277077447829146</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-0.07096153232249058</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-0.05651151506407626</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.02533937341921177</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-0.01794594927044724</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.3208215708000193</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-0.04327203537245961</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-0.06637153696099318</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-0.101929980561037</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-0.07383548215991986</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-0.07636018086202512</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-0.02617868341978191</v>
+      </c>
+      <c r="R27" t="n">
+        <v>-0.04371799949119648</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.07034533291514222</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.04162198424047325</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.05302752417403145</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.0124776331182499</v>
+      </c>
+      <c r="W27" t="n">
+        <v>-0.02558684360084751</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-0.1041616920340367</v>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="n">
+        <v>-0.02508109937556213</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-0.04407307345816491</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>-0.03627487548951525</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>-0.04914977644589325</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>-0.06515613329041692</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>-0.1007628621473939</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>-0.08282153229868428</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>-0.06613696418323389</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>-0.0735219509951115</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>-0.06494220952628105</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>-0.1014060506988903</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>-0.1248537301727897</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>-0.07310057779455548</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>-0.05304822873048654</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>-0.1171533667841516</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0.08863791611341121</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0.04700805048669032</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0.03807009363715874</v>
+      </c>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="n">
+        <v>0.0464985947902683</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AU27" t="n">
+        <v>0.003713893745337593</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>-0.01118819102449908</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>-0.04589632062864002</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>-0.05649132765284826</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>-0.06609488844649203</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>-0.04644188262316717</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>-0.04344386389311428</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>-0.05765012136057468</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>-0.03940385408389702</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>-0.01133458127975118</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>-0.05192574647991233</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>-0.05268456739032956</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>-0.3086589384277207</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>0.05490762807660943</v>
+      </c>
+      <c r="BI27" t="inlineStr"/>
+      <c r="BJ27" t="inlineStr"/>
+      <c r="BK27" t="n">
+        <v>-0.0374953484076217</v>
+      </c>
+      <c r="BL27" t="inlineStr"/>
+      <c r="BM27" t="n">
+        <v>-0.04159410251858109</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>-0.06356609967013505</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>-0.04850418240016907</v>
+      </c>
+      <c r="BP27" t="inlineStr"/>
+      <c r="BQ27" t="inlineStr"/>
+      <c r="BR27" t="inlineStr"/>
+      <c r="BS27" t="n">
+        <v>-0.08274185094756525</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>-0.09400462284285549</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>0.02489546753073935</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>0.1721990111210028</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>0.006850972922866738</v>
+      </c>
+      <c r="BX27" t="inlineStr"/>
+      <c r="BY27" t="n">
+        <v>0.04546237407675768</v>
+      </c>
+      <c r="BZ27" t="n">
+        <v>0.1325889145422421</v>
+      </c>
+      <c r="CA27" t="n">
+        <v>-0.05388137127455739</v>
+      </c>
+      <c r="CB27" t="n">
+        <v>-0.07977370968939912</v>
+      </c>
+      <c r="CC27" t="n">
+        <v>-0.05794794556273786</v>
+      </c>
+      <c r="CD27" t="n">
+        <v>-0.03842752444086717</v>
+      </c>
+      <c r="CE27" t="n">
+        <v>-0.03520927308059463</v>
+      </c>
+      <c r="CF27" t="n">
+        <v>-0.0141060353236071</v>
+      </c>
+      <c r="CG27" t="n">
+        <v>-0.04555879165629406</v>
+      </c>
+      <c r="CH27" t="n">
+        <v>-0.03721826274471773</v>
+      </c>
+      <c r="CI27" t="n">
+        <v>-0.01833667675491846</v>
+      </c>
+      <c r="CJ27" t="n">
+        <v>0.01080350554045761</v>
+      </c>
+      <c r="CK27" t="n">
+        <v>-0.009601286541738752</v>
+      </c>
+      <c r="CL27" t="n">
+        <v>-0.01228361901810437</v>
+      </c>
+      <c r="CM27" t="n">
+        <v>-0.02262082817542233</v>
+      </c>
+      <c r="CN27" t="n">
+        <v>-0.05297464305434119</v>
+      </c>
+      <c r="CO27" t="n">
+        <v>-0.07688605076553845</v>
+      </c>
+      <c r="CP27" t="n">
+        <v>-0.0009958139757388906</v>
+      </c>
+      <c r="CQ27" t="inlineStr"/>
+      <c r="CR27" t="n">
+        <v>-0.3448016254330293</v>
+      </c>
+      <c r="CS27" t="n">
+        <v>0.03536714383729134</v>
+      </c>
+      <c r="CT27" t="inlineStr"/>
+      <c r="CU27" t="n">
+        <v>-0.1303849742567591</v>
+      </c>
+      <c r="CV27" t="n">
+        <v>-0.1290429024329551</v>
+      </c>
+      <c r="CW27" t="n">
+        <v>-0.07040707037072913</v>
+      </c>
+      <c r="CX27" t="n">
+        <v>-0.167668507261534</v>
+      </c>
+      <c r="CY27" t="inlineStr"/>
+      <c r="CZ27" t="n">
+        <v>-0.1560005485608116</v>
+      </c>
+      <c r="DA27" t="n">
+        <v>-0.1177870040442066</v>
+      </c>
+      <c r="DB27" t="inlineStr"/>
+      <c r="DC27" t="n">
+        <v>0.1413541183057312</v>
+      </c>
+      <c r="DD27" t="n">
+        <v>-0.03639238531663835</v>
+      </c>
+      <c r="DE27" t="n">
+        <v>-0.1128879430899872</v>
+      </c>
+      <c r="DF27" t="inlineStr"/>
+      <c r="DG27" t="n">
+        <v>0.08944053546051745</v>
+      </c>
+      <c r="DH27" t="inlineStr"/>
+      <c r="DI27" t="n">
+        <v>-0.0365144463664242</v>
+      </c>
+      <c r="DJ27" t="n">
+        <v>-0.0713262215899535</v>
+      </c>
+      <c r="DK27" t="n">
+        <v>-0.03178892346403028</v>
+      </c>
+      <c r="DL27" t="n">
+        <v>0.05193702254544785</v>
+      </c>
+      <c r="DM27" t="n">
+        <v>-0.05767033194423288</v>
+      </c>
+      <c r="DN27" t="n">
+        <v>-0.01613009748033356</v>
+      </c>
+      <c r="DO27" t="n">
+        <v>0.05696873456386786</v>
+      </c>
+      <c r="DP27" t="n">
+        <v>-0.04045360073510729</v>
+      </c>
+      <c r="DQ27" t="n">
+        <v>-0.07272250858831875</v>
+      </c>
+      <c r="DR27" t="n">
+        <v>-0.003060085055819783</v>
+      </c>
+      <c r="DS27" t="n">
+        <v>0.01408115555599565</v>
+      </c>
+      <c r="DT27" t="n">
+        <v>-0.07229456485877606</v>
+      </c>
+      <c r="DU27" t="inlineStr"/>
+      <c r="DV27" t="n">
+        <v>0.03230316296483604</v>
+      </c>
+      <c r="DW27" t="inlineStr"/>
+      <c r="DX27" t="inlineStr"/>
+      <c r="DY27" t="n">
+        <v>-0.08296305177026575</v>
+      </c>
+      <c r="DZ27" t="n">
+        <v>-0.03203771518835818</v>
+      </c>
+      <c r="EA27" t="n">
+        <v>0.06221656965597777</v>
+      </c>
+      <c r="EB27" t="n">
+        <v>-0.1064968732280605</v>
+      </c>
+      <c r="EC27" t="inlineStr"/>
+      <c r="ED27" t="n">
+        <v>0.01509357049460647</v>
+      </c>
+      <c r="EE27" t="inlineStr"/>
+      <c r="EF27" t="n">
+        <v>-0.01654753698253053</v>
+      </c>
+      <c r="EG27" t="n">
+        <v>0.1350406334497727</v>
+      </c>
+      <c r="EH27" t="n">
+        <v>-0.03051478996646484</v>
+      </c>
+      <c r="EI27" t="n">
+        <v>-0.07832353095979094</v>
+      </c>
+      <c r="EJ27" t="n">
+        <v>-0.06680051185090097</v>
+      </c>
+      <c r="EK27" t="n">
+        <v>-0.07303428809887347</v>
+      </c>
+      <c r="EL27" t="n">
+        <v>-0.06059256488331943</v>
+      </c>
+      <c r="EM27" t="n">
+        <v>-0.05504327253493635</v>
+      </c>
+      <c r="EN27" t="n">
+        <v>-0.07311830682563958</v>
+      </c>
+      <c r="EO27" t="n">
+        <v>-0.04325778041885275</v>
+      </c>
+      <c r="EP27" t="n">
+        <v>-0.02243035370099822</v>
+      </c>
+      <c r="EQ27" t="n">
+        <v>-0.04506067495896104</v>
+      </c>
+      <c r="ER27" t="n">
+        <v>0.02767703694805945</v>
+      </c>
+      <c r="ES27" t="n">
+        <v>-0.03098524128166513</v>
+      </c>
+      <c r="ET27" t="n">
+        <v>-0.1188661908645852</v>
+      </c>
+      <c r="EU27" t="n">
+        <v>-0.02184423565265092</v>
+      </c>
+      <c r="EV27" t="n">
+        <v>-0.007254915118879879</v>
+      </c>
+      <c r="EW27" t="n">
+        <v>0.01515676008943867</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
